--- a/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A214"/>
+  <dimension ref="A1:A188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,7 +480,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/ravindra-chavan-elected-maharashtra-bjp-president-ahead-of-crucial-mumbai-civic-body-polls/articleshow/122185741.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/dombivli-mla-ravindra-chavan-to-be-appointed-maharashtra-bjp-prez-23582620</t>
         </is>
       </c>
     </row>
@@ -494,1435 +494,1253 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/dombivli-mla-ravindra-chavan-to-be-appointed-maharashtra-bjp-prez-23582620</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/dombivli-pride-2025-grand-dahi-handi-celebrates-janmashtami-bjp-leader-ravindra-chavan-urges-youth-to-drive-maharashtras-growth/articleshow/123332580.cms</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/dombivli-pride-2025-grand-dahi-handi-celebrates-janmashtami-bjp-leader-ravindra-chavan-urges-youth-to-drive-maharashtras-growth/articleshow/123332580.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ravindra-chavan-set-to-be-bjp-state-president-101751310615190.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ravindra-chavan-set-to-be-bjp-state-president-101751310615190.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ravindra-chavan-to-be-new-bjp-chief-for-maharashtra-3609432</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ravindra-chavan-to-be-new-bjp-chief-for-maharashtra-3609432</t>
+          <t>https://www.etvbharat.com/en/!state/meeting-with-ravindra-chavan-personal-not-political-maharashtra-congress-leader-kunal-patil-dismisses-bjp-switch-rumours-enn25062503849</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/meeting-with-ravindra-chavan-personal-not-political-maharashtra-congress-leader-kunal-patil-dismisses-bjp-switch-rumours-enn25062503849</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-unanimously-elected-as-new-maharashtra-bjp-president-23582746</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-unanimously-elected-as-new-maharashtra-bjp-president-23582746</t>
+          <t>https://www.financialexpress.com/india-news/who-is-ravindra-chavan-four-time-mla-appointed-as-maharashtra-units-new-president/3899457/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/india-news/who-is-ravindra-chavan-four-time-mla-appointed-as-maharashtra-units-new-president/3899457/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/hindutva-not-against-any-religion-treating-all-religions-equally-is-true-secularism-nitin-gadkari-3611385</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/hindutva-not-against-any-religion-treating-all-religions-equally-is-true-secularism-nitin-gadkari-3611385</t>
+          <t>https://zeenews.india.com/india/who-is-ravindra-chavan-new-maharashtra-bjp-chief-close-confidant-of-cm-devendra-fadnavis-2925029.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/who-is-ravindra-chavan-new-maharashtra-bjp-chief-close-confidant-of-cm-devendra-fadnavis-2925029.html</t>
+          <t>https://www.moneycontrol.com/news/india/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-civic-polls-13214817.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-civic-polls-13214817.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/justice-chavan-calls-for-national-judicial-service-reforms-to-address-vacancies-in-judiciary/articleshow/121299899.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/viral-list-of-dist-chiefs-fake-bjp-warns-of-police-action/articleshow/121252533.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-files-nomination-for-post-of-maharashtra-bjp-president-23582507</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/justice-chavan-calls-for-national-judicial-service-reforms-to-address-vacancies-in-judiciary/articleshow/121299899.cms</t>
+          <t>https://www.ptinews.com/story/national/ex-minister-ravindra-chavan-is-bjp's-new-maharashtra-unit-chief/2690729</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-files-nomination-for-post-of-maharashtra-bjp-president-23582507</t>
+          <t>https://www.deccanherald.com/india/india-political-updates-latest-pm-narendra-modi-arvind-kejriwal-atishi-sanjay-singh-aap-bjp-congress-rahul-gandhi-delhi-assembly-elections-polls-live-politics-news-3350792</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ex-minister-ravindra-chavan-is-bjp's-new-maharashtra-unit-chief/2690729</t>
+          <t>https://www.deccanherald.com/india/maharashtra/amit-shah-to-begin-3-day-maharashtra-visit-ahead-of-local-body-polls-3556463</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/money-lender-booked-for-suicide-abetment-of-debtor/articleshow/121603123.cms</t>
+          <t>https://www.nagpurtoday.in/ravindra-chavan-appointed-maharashtra-bjp-president/07021333</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/india-political-updates-latest-pm-narendra-modi-arvind-kejriwal-atishi-sanjay-singh-aap-bjp-congress-rahul-gandhi-delhi-assembly-elections-polls-live-politics-news-3350792</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/amit-shah-to-begin-3-day-maharashtra-visit-ahead-of-local-body-polls-3556463</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/58-bjp-chiefs-of-districts-named/articleshow/121146293.cms</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/58-bjp-chiefs-of-districts-named/articleshow/121146293.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-chief-in-maharashtra-brings-mns-union-workers-into-party/articleshow/123367896.cms</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/ravindra-chavan-appointed-maharashtra-bjp-president/07021333</t>
+          <t>https://www.msn.com/en-in/news/India/ameet-satam-becomes-bjp-s-new-mumbai-chief-ahead-of-bmc-polls-who-is-he/ar-AA1L9t6x</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-chief-in-maharashtra-brings-mns-union-workers-into-party/articleshow/123367896.cms</t>
+          <t>https://www.mid-day.com/news/india-news/article/indrayani-river-bridge-collapse-ex-minister-seeks-probe-into-delay-in-construction-of-new-structure-23571125</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/indrayani-river-bridge-collapse-ex-minister-seeks-probe-into-delay-in-construction-of-new-structure-23571125</t>
+          <t>https://www.newsband.in/article_detail/dombivli-residents-demand-clarity-as-railways-issue-eviction-notices</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/dombivli-residents-demand-clarity-as-railways-issue-eviction-notices</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bjps-sankalp-to-siddhi-campaign-to-begin-this-week/articleshow/121606429.cms</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/indigos-agile-employees-secure-record-salary-hike-in-historic-agreement-with-union/</t>
+          <t>https://tennews.in/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/bodies-of-pahalgam-terror-attack-victims-from-maharashtra-brought-to-mumbai-enn25042305870</t>
+          <t>https://www.ptinews.com/editor-detail/Pune-Congress-leader-Sanjay-Jagtap-joins-BJP/2733730</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra/ar-AA1JFbMn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://thecsrjournal.in/indigos-agile-employees-secure-record-salary-hike-in-historic-agreement-with-union/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/07/31/bes7-mh-bjp-meeting.html</t>
+          <t>https://www.socialnews.xyz/?p=6725428</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/ravindra-chavan-a-visionary-leader-strengthening-maharashtra-bjps-political-landscape.html</t>
+          <t>https://gallinews.com/ravindra-chavan-bane-bjp-ke-naye-maharashtra-president/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/news/india/ravindra-chavan-to-lead-maharashtra-bjp-telangana-andhra-uttarakhand-unit-chiefs-to-be-named-tomorrow-1784254</t>
+          <t>https://www.afternoonvoice.com/bjp-picks-ravindra-chavan-as-maharashtra-chief-ahead-of-key-civic-polls.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6725428</t>
+          <t>https://theindianawaaz.com/ravindra-chavan-appointed-as-bjp-state-president-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/bjp-picks-ravindra-chavan-as-maharashtra-chief-ahead-of-key-civic-polls.html</t>
+          <t>https://www.cityairnews.com/content/ravindra-chavan-elected-unopposed-as-maha-bjp-chief</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/ravindra-chavan-set-take-over-maharashtra-unit-bjp-chief-tomorrow-424218</t>
+          <t>https://www.punekarnews.in/pune-kundmala-bridge-collapses-5-days-after-rs-8-crore-renovation-approval-sanjay-raut-alleges-corruption-claims-only-rs-80000-was-actually-sanctioned/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://tennews.in/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-local-election-bjp-president-ravindra-chavan-asked-former-mps-and-mlas-to-adopt-one-mandal-each-ann-2988472</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/ravindra-chavan-appointed-as-bjp-state-president-of-maharashtra/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-appointed-ravindra-chavan-as-working-state-president-of-maharashtra-know-his-journey/articleshow/117154523.cms</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.cityairnews.com/content/ravindra-chavan-elected-unopposed-as-maha-bjp-chief</t>
+          <t>https://www.aajtak.in/topic/ravindra-chavan</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-local-election-bjp-president-ravindra-chavan-asked-former-mps-and-mlas-to-adopt-one-mandal-each-ann-2988472</t>
+          <t>https://www.livehindustan.com/national/why-bjp-gave-responsibility-of-maharashtra-unit-to-ravindra-chavan-maratha-face-201736616683779.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-appointed-ravindra-chavan-as-working-state-president-of-maharashtra-know-his-journey/articleshow/117154523.cms</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-chief-of-maharashtra-bjp-ravindra-chavan-name-is-almost-finalised-9348436.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/topic/ravindra-chavan</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-ravindra-chavan-can-become-president-of-maharashtra-bjp-mumbai-ann-2969682</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-chief-of-maharashtra-bjp-ravindra-chavan-name-is-almost-finalised-9348436.html</t>
+          <t>https://ndtv.in/india/ravindra-chavan-from-maharashtra-khandelwal-from-mp-became-new-state-president-of-bjp-know-all-details-here-8812249</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/why-bjp-gave-responsibility-of-maharashtra-unit-to-ravindra-chavan-maratha-face-201736616683779.html</t>
+          <t>https://www.jansatta.com/national/bjp-may-appoint-ravindra-chavan-maharashtra-state-president-cm-devendra-fadnavis/3775586/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-ravindra-chavan-can-become-president-of-maharashtra-bjp-mumbai-ann-2969682</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-why-party-appointed-know-all/articleshow/117210600.cms</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/ravindra-chavan-from-maharashtra-khandelwal-from-mp-became-new-state-president-of-bjp-know-all-details-here-8812249</t>
+          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-name-suggested-as-maharashtra-bjp-president-by-chandrashekhar-bawankule-2971280</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/bjp-may-appoint-ravindra-chavan-maharashtra-state-president-cm-devendra-fadnavis/3775586/</t>
+          <t>https://ndtv.in/maharashtra-news/ravindra-chavan-new-maharashtra-bjp-president-know-his-political-journey-8811120</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-why-party-appointed-know-all/articleshow/117210600.cms</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-ravindra-chavan-warns-throw-away-the-list-of-81-district-presidents-of-bjp-don-t-make-it-viral-social-media-1359706</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/maharashtra/mumbai-ravindra-chavan-will-be-the-new-president-of-maharashtra-bjp-nomination-filed-in-the-presence-of-kiren-rijiju-23971616.html</t>
+          <t>https://www.lokmatnews.in/india/who-is-ravindra-chavan-bjp-mla-appointed-working-state-president-maharashtra-replace-chandrashekhar-bawankule-b507/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-name-suggested-as-maharashtra-bjp-president-by-chandrashekhar-bawankule-2971280</t>
+          <t>https://marathi.ndtv.com/cities/kalyan-ex-bjp-mla-feud-viral-clip-shows-strong-words-against-kapil-patil-and-ravindra-chavan-in-heated-exchange-9007785</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-appointed-maharashtra-bjp-working-president-cm-devendra-fadnavis-welcomes-2861067</t>
+          <t>https://mandalnews.com/maharashtra/ravindra-chauhan-on-the-post-of-bjp-maharashtra-state-president/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/ravindra-chavan-new-maharashtra-bjp-president-know-his-political-journey-8811120</t>
+          <t>https://marathi.ndtv.com/cities/bjp-news-ravindra-chavan-appointed-bjps-maharashtra-working-president-7451905</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-ravindra-chavan-warns-throw-away-the-list-of-81-district-presidents-of-bjp-don-t-make-it-viral-social-media-1359706</t>
+          <t>https://marathi.ndtv.com/politics/bjp-state-president-ravindra-chavan-makes-big-statement-on-alliance-with-uddhav-thackeray-8864806</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/kalyan-ex-bjp-mla-feud-viral-clip-shows-strong-words-against-kapil-patil-and-ravindra-chavan-in-heated-exchange-9007785</t>
+          <t>https://marathi.ndtv.com/politics/ravindra-chavan-opens-up-about-disappointment-over-eknath-shinde-becoming-chief-minister-reveals-true-feelings-8865262</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/who-is-ravindra-chavan-bjp-mla-appointed-working-state-president-maharashtra-replace-chandrashekhar-bawankule-b507/</t>
+          <t>https://mandalnews.com/amravati/maharashtra-council-established-for-1-5-lakh-marathi-speakers/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/bjp-maharashtra-president-ravindra-chavan-kunal-patil-congress-north-maharashtra-dhule-ntcpbt-dskc-2277786-2025-07-02</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-brahmin-obc-maratha-formula-ravindra-chouhan-chandrashekhar-bawankule-8954968.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/maharashtra/ravindra-chauhan-on-the-post-of-bjp-maharashtra-state-president/</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-elected-as-bjp-working-state-president-maharashtra-politics-marathi-news-1338059</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/bjp-state-president-ravindra-chavan-makes-big-statement-on-alliance-with-uddhav-thackeray-8864806</t>
+          <t>https://marathi.ndtv.com/politics/bjp-state-working-president-ravindra-chavan-responds-congress-state-president-harshvardhan-sapkal-8802075</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/ravindra-chavan-opens-up-about-disappointment-over-eknath-shinde-becoming-chief-minister-reveals-true-feelings-8865262</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-politics-bjp-leader-ravindra-chavan-unanimously-elected-maharashtra-bjp-president-80826</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ravindra-chavan-is-now-president-of-bjp-maharashtra-state-know-about-his-political-career-scj-81-5196879/</t>
+          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-appointed-as-bjp-state-working-president-by-j-p-nadda/articleshow/117154533.cms</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/maharashtra-council-established-for-1-5-lakh-marathi-speakers/</t>
+          <t>https://news18marathi.com/maharashtra/ravindra-chavan-to-be-new-maharashtra-bjp-president-show-of-power-at-aaditya-thackeray-constituency-1425668.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/bjp-news-ravindra-chavan-appointed-bjps-maharashtra-working-president-7451905</t>
+          <t>https://www.msn.com/mr-in/news/other/bjp-ravindra-chavan-news-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%9F-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-maharashtra-politics/vi-AA1K12wX</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-brahmin-obc-maratha-formula-ravindra-chouhan-chandrashekhar-bawankule-8954968.html</t>
+          <t>https://www.navarashtra.com/maharashtra/new-bjp-maharashtra-state-president-ravindra-chavan-political-journey-complete-information-marathi-916730.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-elected-as-bjp-working-state-president-maharashtra-politics-marathi-news-1338059</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/3/the-theme-of-the-dombivalikar-friendship-run-was-unveiled-by-bjp-state-president-ravindra-chavan.html</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/bjp-state-working-president-ravindra-chavan-responds-congress-state-president-harshvardhan-sapkal-8802075</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/30/from-party-worker-to-state-president.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/youtuber-shirish-gavas-passed-away-red-soil-stories-channel-33-year-old-founder-died-19834284</t>
+          <t>https://marathi.ndtv.com/politics/mahayuti-news-unveiling-of-chhatrapati-shivaji-maharaj-statue-in-dombivli-shiv-sena-shinde-faction-criticizes-bjp-mla-ravindra-chavan-7945018</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/annasaheb-dange-joins-bjp-with-his-two-sons-chiman-and-vishwanath-dange-in-the-presence-of-cm-devendra-fadnavis-ann-2987987</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bjp-leadership-meet-ravindra-chavan-meets-jp-nadda-in-delhi-first-meeting-as-state-president-earlier-met-amit-shah-in-pune-1368594</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-politics-bjp-leader-ravindra-chavan-unanimously-elected-maharashtra-bjp-president-80826</t>
+          <t>https://www.navarashtra.com/maharashtra/not-a-single-resident-of-65-buildings-in-kalyan-dombivli-will-be-allowed-to-become-homeless-assures-ravindra-chavan-817558.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/congress-mp-ravindra-chavan-warning-to-follow-protocol-due-to-nanded-municipal-corporation-commissioner-over-not-inviting-for-programme-1360903</t>
+          <t>https://www.localnewsnetwork.in/bjp-needs-a-mayor-to-remove-the-development-eclipse-of-kalyan-dombivali-bjp-state-president-ravindra-chavan/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-appointed-as-bjp-state-working-president-by-j-p-nadda/articleshow/117154533.cms</t>
+          <t>https://www.navarashtra.com/maharashtra/regarding-the-stalled-redevelopment-case-of-shantidoot-housing-society-and-lig-1-buildings-in-kalyan-956786.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/bjp-announces-new-state-presidents-in-4-states-changes-in-maharashtra-uttarakhand-telangana-and-himachal-pradesh/articleshow/122163940.cms</t>
+          <t>https://marathi.abplive.com/tv-show/majha-vishesh/maharashtra-bjp-president-ravindra-chavan-s-first-interview-reveals-role-in-operation-shinde-discusses-mahayuti-election-strategy-it-notices-and-marathi-politics-1369435</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/bjp-will-get-a-new-maharashtra-president-ravindra-chavan-will-be-appointed-in-place-of-chandrashekhar-bawankule-1366663</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-and-local-body-polls/articleshow/122185894.cms</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/ravindra-chavan-to-be-new-maharashtra-bjp-president-show-of-power-at-aaditya-thackeray-constituency-1425668.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/ravindra-chavan-says-thanks-to-his-party-after-selected-for-bjp-maharashtra-president/articleshow/122185577.cms</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/bjp-ravindra-chavan-news-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%9F-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-maharashtra-politics/vi-AA1K12wX</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/31/adopt-one-mandal-each-and-resolve-to-build-an-organization-state-president-ravindra-chavan-appeals-to-former-m.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/ravindra-chavan-bjp-new-president-profile-dombivli-mla-maharashtra-mumbai-politics-marathi-news-1367337</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-exclusive-interview-talk-about-will-there-be-challenge-to-bjp-if-raj-thackeray-uddhav-thackeray-come-together-maharashtra-politics-marathi-news-1369421</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/3/the-theme-of-the-dombivalikar-friendship-run-was-unveiled-by-bjp-state-president-ravindra-chavan.html</t>
+          <t>https://news18marathi.com/maharashtra/ravindra-chavan-political-masterstroke-ulhasnagar-sharad-pawar-group-breakdown-1445668.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/30/from-party-worker-to-state-president.html</t>
+          <t>https://www.navarashtra.com/maharashtra/bjp-leader-ravindra-chavan-express-feeelings-after-become-a-bjp-maharashtra-president-916809.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/mahayuti-news-unveiling-of-chhatrapati-shivaji-maharaj-statue-in-dombivli-shiv-sena-shinde-faction-criticizes-bjp-mla-ravindra-chavan-7945018</t>
+          <t>https://marathi.abplive.com/news/politics/congress-leader-kailash-gorantyal-and-suresh-varpudkar-will-join-bjp-under-the-leadership-of-state-president-ravindra-chavan-at-mumbai-jalna-constituency-before-election-1373052</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/mumbai-metro/video/bjp-appointed-ravindra-chavan-as-maharashtra-unit-cheif-mumbai-metro-frvd-2277550-2025-07-02</t>
+          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-may-be-elected-as-bjp-state-president-for-maharashtra-marathi-news/articleshow/122124651.cms</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bjp-leadership-meet-ravindra-chavan-meets-jp-nadda-in-delhi-first-meeting-as-state-president-earlier-met-amit-shah-in-pune-1368594</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-amit-satam-elected-as-mumbai-president-of-bjp-cm-devendra-fadnavis-9153593</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-former-congress-mla-kunal-patil-likely-to-join-bjp-meets-ravindra-chavan-in-mumbai-marathi-news-1365750</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-bjp-calls-urgent-meeting-in-mumbai-raj-thackeray-takes-aggressive-stance-on-matak-sodi-allegations-1379525</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/bjp-needs-a-mayor-to-remove-the-development-eclipse-of-kalyan-dombivali-bjp-state-president-ravindra-chavan/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-politics-1500-members-of-uddhav-thackerays-party-join-bjp-party-entry-in-mumbai-in-the-presence-of-ravindra-chavan/910127</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/tv-show/majha-vishesh/maharashtra-bjp-president-ravindra-chavan-s-first-interview-reveals-role-in-operation-shinde-discusses-mahayuti-election-strategy-it-notices-and-marathi-politics-1369435</t>
+          <t>https://www.mymahanagar.com/mahamumbai/dahi-handi-2025-dahi-handi-celebrated-in-a-traditional-manner-in-dombivli-bjp-mla-ravindra-chavan/912575/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-and-local-body-polls/articleshow/122185894.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nanded/set-back-for-bjp-ashok-chavan-discussion-on-alliance-between-congress-and-prakash-ambedkar-vanchit-bahujan-aghadi/articleshow/122873066.cms</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/ravindra-chavan-says-thanks-to-his-party-after-selected-for-bjp-maharashtra-president/articleshow/122185577.cms</t>
+          <t>https://marathi.abplive.com/news/nanded/nanded-news-congress-and-vanchit-hint-at-alliance-for-local-government-elections-in-nanded-will-consider-proposal-if-received-1371522</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ravindra-chavan-elected-unopposed-as-bjp-state-president-formal-announcement-today-mumbai-print-news-ssb-93-5194361/</t>
+          <t>https://www.tarunbharat.com/youth-leader-vishal-parab-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/31/adopt-one-mandal-each-and-resolve-to-build-an-organization-state-president-ravindra-chavan-appeals-to-former-m.html</t>
+          <t>https://www.navarashtra.com/politics/congress-may-alliance-with-vba-party-in-nanded-for-upcoming-municipal-election-942211.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-exclusive-interview-talk-about-will-there-be-challenge-to-bjp-if-raj-thackeray-uddhav-thackeray-come-together-maharashtra-politics-marathi-news-1369421</t>
+          <t>https://www.etvbharat.com/mr/!state/shetkari-kamgar-paksha-skp-jayant-patils-brother-pandit-patil-to-join-bjp-mumbai-maharashtra-maharashtra-news-mhs25041603477</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/ravindra-chavan-political-masterstroke-ulhasnagar-sharad-pawar-group-breakdown-1445668.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/raigad/shivsena-mla-mahendra-thorve-join-bjp-in-raigad-before-local-government-elections-marathi-news/articleshow/121927356.cms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/congress-leader-kailash-gorantyal-and-suresh-varpudkar-will-join-bjp-under-the-leadership-of-state-president-ravindra-chavan-at-mumbai-jalna-constituency-before-election-1373052</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/former-congress-mla-kailash-gorantyal-joins-bjp-major-challenge-for-shinde-led-shiv-sena-in-jalna/articleshow/123019959.cms</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-may-be-elected-as-bjp-state-president-for-maharashtra-marathi-news/articleshow/122124651.cms</t>
+          <t>https://www.dainikprabhat.com/bjp-will-soon-get-a-new-state-president-ravindra-chavan-will-be-entrusted-with-the-responsibility/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-amit-satam-elected-as-mumbai-president-of-bjp-cm-devendra-fadnavis-9153593</t>
+          <t>https://marathi.asianetnews.com/maharashtra/ravindra-chavan-new-bjp-maharashtra-president/articleshow-x7qax8g</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-bjp-calls-urgent-meeting-in-mumbai-raj-thackeray-takes-aggressive-stance-on-matak-sodi-allegations-1379525</t>
+          <t>https://www.dainikprabhat.com/bjp-will-get-a-new-state-president-today-ravindra-chavan-will-accept-the-oath/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/photogallery/news/ravindra-chavan-important-role-when-eknath-shinde-takeover-shiv-sena/photoshow/122188079.cms</t>
+          <t>https://civicmirror.in/maharashtra/four-former-corporators-of-ubatha-in-malvan-join-bjp-along-with-their-supporters/cid1752483678.htm</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/amit-satam-on-becoming-mumbai-bjp-president/935016</t>
+          <t>https://www.marathiebatmya.com/political/activist-of-ubt-sharad-pawar-group-and-congress-in-shahapur-taluka-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/dahi-handi-2025-dahi-handi-celebrated-in-a-traditional-manner-in-dombivli-bjp-mla-ravindra-chavan/912575/</t>
+          <t>https://www.marathiebatmya.com/political/many-former-corporators-from-kalyan-dombivli-chandrapur-districts-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sudhakar-badgujar-bjp-chandrashekhar-bawankule-he-join-bjp-with-girish-mahajan-and-ravindra-chavan-1364736</t>
+          <t>https://www.timemaharashtra.com/maharashtra/big-news-ravindra-chavan-elected-as-bjps-working-regional-president/108447/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nanded/set-back-for-bjp-ashok-chavan-discussion-on-alliance-between-congress-and-prakash-ambedkar-vanchit-bahujan-aghadi/articleshow/122873066.cms</t>
+          <t>https://deshonnati.com/bjp-president-banner-tore-the-of-state-election/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/nanded-news-congress-and-vanchit-hint-at-alliance-for-local-government-elections-in-nanded-will-consider-proposal-if-received-1371522</t>
+          <t>https://news34.in/2025/07/ravindra-shinde-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/claiming-that-rs-8-crore-was-approved-for-the-indrayani-river-bridge-sanjay-raut-showed-only-a-letter-for-rs-80-thousand-devendra-fadnavis-1364502</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-ravindra-chavan-talks-on-uddhav-thackeray-raj-thackeray-reunite-bmc-elections-2025/articleshow/123154745.cms</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/dhule-congress-leader-kunal-patil-dismisses-rumors-of-joining-bjp-maharashtra-news-mhs25062501797</t>
+          <t>https://www.mymahanagar.com/maharashtra/the-election-of-bjp-state-president-will-be-held-on-july-1-and-ravindra-chavan-is-likely-to-be-the-candidate/897175/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/youth-leader-vishal-parab-joins-bjp/</t>
+          <t>https://news18marathi.com/mumbai/ravindra-chavan-has-become-the-new-bjp-maharashtra-president-1426306.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!politics/bmc-election-2025-major-reshuffle-in-bjp-amit-satam-appointed-as-president-of-mumbai-bjp-know-political-reactions-his-profile-coroporate-job-to-politician-mhs25082501410</t>
+          <t>https://www.mymahanagar.com/photo-gallery/ravindra-chavan-appealed-to-the-workers-after-assuming-the-post-of-bjp-state-president/898007/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/shetkari-kamgar-paksha-skp-jayant-patils-brother-pandit-patil-to-join-bjp-mumbai-maharashtra-maharashtra-news-mhs25041603477</t>
+          <t>https://marathi.abplive.com/videos/news/politics-bjp-maharashtra-state-president-election-nomination-process-begins-ravindra-chavhan-likely-to-secure-position-1367011</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-misssion-mumbai-bjp-will-turn-the-tables-meeting-for-the-post-of-mumbai-president-on-place-of-ashish-shelar-two-mlas-put-forward-their-names-pravin-darekar-1354321</t>
+          <t>https://www.marathiebatmya.com/political/former-nagsevaks-and-activists-of-bva-of-vasai-virar-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/raigad/shivsena-mla-mahendra-thorve-join-bjp-in-raigad-before-local-government-elections-marathi-news/articleshow/121927356.cms</t>
+          <t>https://pcbtoday.in/%E0%A4%AD%E0%A4%BE%E0%A4%9C%E0%A4%AA%E0%A4%BE-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%BE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B0%E0%A4%B5%E0%A5%80%E0%A4%82/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/former-congress-mla-kailash-gorantyal-joins-bjp-major-challenge-for-shinde-led-shiv-sena-in-jalna/articleshow/123019959.cms</t>
+          <t>https://www.marathiebatmya.com/political/bhor-mulshi-taluka-workers-from-various-parties-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chief-minister-devendra-fadnavis-reaction-regarding-marathi-language-criticism-on-uddhav-thackeray-in-mumbai-1367354</t>
+          <t>https://www.msn.com/en-gb/news/world/kedar-jadhav-makes-bold-prediction-about-india-playing-pakistan-in-asia-cup/ar-AA1KJnU4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/photogallery/news/congress-leader-kunal-patil-may-be-join-bjp-soon/photoshow/122030946.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/4-ex-congress-corporators-join-bjp-in-kalyan-dombivli/articleshow/123447826.cms</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/bjp-will-get-a-new-state-president-today-ravindra-chavan-will-accept-the-oath/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/former-nagsevaks-and-activists-of-bva-of-vasai-virar-join-bjp/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-inducts-key-pwp-leaders-before-local-body-elections-101744831159344.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/four-former-corporators-of-ubatha-in-malvan-join-bjp-along-with-their-supporters/cid1752483678.htm</t>
+          <t>https://www.livemint.com/politics/news/no-one-becomes-great-by-imposing-themselves-nitin-gadkari-warns-against-arrogance-in-leadership-cong-reacts-11752387796290.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/maharashtra/ravindra-chavan-to-become-maharashtra-bjp-president/articleshow-bv2gf6u</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cabinet-reshuffle-on-cards-fadnavis-meets-shah-nadda-in-delhi-3648744</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/bhor-mulshi-taluka-workers-from-various-parties-join-bjp/</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/ncp-shiv-sena-ubt-members-join-bjp-in-nashik/articleshow/122233115.cms</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/activist-of-ubt-sharad-pawar-group-and-congress-in-shahapur-taluka-join-bjp/</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/congress-ex-mla-suresh-warpudkar-and-family-set-to-join-bjp/articleshow/122951927.cms</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-former-corporators-from-kalyan-dombivli-chandrapur-districts-join-bjp/</t>
+          <t>https://www.deccanherald.com/india/bjp-state-chiefs-kharges-high-command-remark-congress-bihar-elections-modi-sonia-rahul-gandhi-socialist-secular-rss-constitution-india-tamil-nadu-3610086</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/big-news-ravindra-chavan-elected-as-bjps-working-regional-president/108447/</t>
+          <t>https://www.nagpurtoday.in/emotional-farewell-outgoing-bjp-state-president-bawankule-pens-heartfelt-letter-to-party-workers/07021355</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/bjp-president-banner-tore-the-of-state-election/</t>
+          <t>https://www.afternoonvoice.com/ravindra-chavan-a-visionary-leader-strengthening-maharashtra-bjps-political-landscape.html</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/07/ravindra-shinde-joins-bjp/</t>
+          <t>https://ommcomnews.com/india-news/congress-receives-a-jolt-after-former-dhule-mla-kunal-patil-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-ravindra-chavan-talks-on-uddhav-thackeray-raj-thackeray-reunite-bmc-elections-2025/articleshow/123154745.cms</t>
+          <t>https://www.bhaskarenglish.in/national/news/bjp-state-presidents-appointment-national-president-election-july-maharashtra-himachal-pm-modi-jp-nadda-135348404.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/the-election-of-bjp-state-president-will-be-held-on-july-1-and-ravindra-chavan-is-likely-to-be-the-candidate/897175/</t>
+          <t>https://english.publictv.in/bjp-announces-new-state-chiefs-in-7-states-2-uts-moves-closer-to-elect-national-president/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/mumbai/ravindra-chavan-has-become-the-new-bjp-maharashtra-president-1426306.html</t>
+          <t>https://www.newsx.com/india/who-is-the-new-bjp-party-president-list-of-state-party-president-out-11032/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/photo-gallery/ravindra-chavan-appealed-to-the-workers-after-assuming-the-post-of-bjp-state-president/898007/</t>
+          <t>https://fox5sandiego.com/business/press-releases/ein-presswire/827256708/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-bjp-maharashtra-state-president-election-nomination-process-begins-ravindra-chavhan-likely-to-secure-position-1367011</t>
+          <t>https://www.ndtv.com/india-news/ex-minister-ravindra-chavan-files-nomination-for-maharashtra-bjp-chief-post-8800476</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/four-former-corporators-of-ubt-in-malvan-join-bjp-along-with-their-supporters-welcomed-by-bjp-state-president-ravindra-chavan-maharashtra-news-mhs25071403115</t>
+          <t>https://www.newsonair.gov.in/bjp-leader-ravindra-chavan-appointed-as-new-state-president-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%AD%E0%A4%BE%E0%A4%9C%E0%A4%AA%E0%A4%BE-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%BE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B0%E0%A4%B5%E0%A5%80%E0%A4%82/</t>
+          <t>https://www.aninews.in/news/national/politics/double-engine-govt-working-in-peoples-best-interests-new-maharashtra-bjp-chief-ravindra-chavan20250702021253/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://fox5sandiego.com/business/press-releases/ein-presswire/827256708/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy</t>
+          <t>https://tennews.in/ravindra-chavan-elected-unopposed-as-maha-bjp-chief/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-gb/news/world/kedar-jadhav-makes-bold-prediction-about-india-playing-pakistan-in-asia-cup/ar-AA1KJnU4</t>
+          <t>https://www.tribuneindia.com/news/business/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/no-one-becomes-great-by-imposing-themselves-nitin-gadkari-flags-arrogance-in-leadership-congress-reacts/ar-AA1IuYys</t>
+          <t>https://ndtv.in/india/who-is-ravindra-chavan-new-bjp-president-for-maharashtra-close-aide-of-cm-fadnavis-8810167</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/4-ex-congress-corporators-join-bjp-in-kalyan-dombivli/articleshow/123447826.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-to-appoints-ravindra-chavan-next-bjp-president-of-maharashtra-chandrashekhar-bawankule-amit-shah-visit-know-all/articleshow/121479121.cms</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-inducts-key-pwp-leaders-before-local-body-elections-101744831159344.html</t>
+          <t>https://www.indiatv.in/maharashtra/maharashtra-ravindra-chavan-set-to-become-new-president-of-state-bjp-said-sources-2025-06-30-1146038</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-visited-sai-baba-in-shirdi-after-being-appointed-as-state-executive-president-of-bjp-maharashtra-marathi-news-1338130</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ahead-of-local-body-polls-bjp-finalises-names-of-22-district-presidents/articleshow/121549544.cms</t>
+          <t>https://www.newsonair.gov.in/mr/ravindra-chavan-elected-unopposed-as-new-state-president-of-bharatiya-janata-party/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/politics/news/no-one-becomes-great-by-imposing-themselves-nitin-gadkari-warns-against-arrogance-in-leadership-cong-reacts-11752387796290.html</t>
+          <t>https://hindi.webdunia.com/maharashtra/who-is-maharashtra-bjp-new-president-ravindra-chavan-know-125070100083_1.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
+          <t>https://ndtv.in/india/hemant-khandelwal-will-be-the-new-president-of-madhya-pradesh-bjp-8808221</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cabinet-reshuffle-on-cards-fadnavis-meets-shah-nadda-in-delhi-3648744</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-bjp-likely-to-contest-alone-amid-mumbai-bmc-polls-with-eknath-shinde-and-ajit-pawar-amit-shah-ravindra-chavan-meet/articleshow/122897869.cms</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-names-22-more-district-chiefs-ahead-of-civic-polls/articleshow/121541000.cms</t>
+          <t>https://navbharattimes.indiatimes.com/india/bjp-announces-new-state-presidents-in-4-states-changes-in-maharashtra-uttarakhand-telangana-and-himachal-pradesh/articleshow/122163940.cms</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/ncp-shiv-sena-ubt-members-join-bjp-in-nashik/articleshow/122233115.cms</t>
+          <t>https://marathi.abplive.com/news/pune/pune-news-sanjay-jagtap-joins-bjp-ravindra-chavan-s-presence-big-blow-to-congress-before-upcoming-elections-1370379</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/congress-ex-mla-suresh-warpudkar-and-family-set-to-join-bjp/articleshow/122951927.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-maharashtra-annouces-50-district-president-navi-mumbai-rajesh-patil-mira-bhayandar-dilip-jain-check-full-list/articleshow/121136990.cms</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/bjp-state-chiefs-kharges-high-command-remark-congress-bihar-elections-modi-sonia-rahul-gandhi-socialist-secular-rss-constitution-india-tamil-nadu-3610086</t>
+          <t>https://www.abplive.com/states/maharashtra/parbhani-congress-leader-suresh-warpudkar-joins-bjp-with-supporters-ahead-of-nagar-nikay-chunav-2987557</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/emotional-farewell-outgoing-bjp-state-president-bawankule-pens-heartfelt-letter-to-party-workers/07021355</t>
+          <t>https://marathi.abplive.com/videos/news/bjp-maharashtra-ravindra-chavan-set-to-be-elected-as-state-president-unopposed-formal-announcement-expected-tomorrow-1367175</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/congress-receives-a-jolt-after-former-dhule-mla-kunal-patil-joins-bjp/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-maharashtra-bjp-president-likely-to-contest-mumbai-cricket-association-mca-election-in-november-after-delhi-visit-1374335</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/bjp-state-presidents-appointment-national-president-election-july-maharashtra-himachal-pm-modi-jp-nadda-135348404.html</t>
+          <t>https://thefocusindia.com/maharashtra-news/ravindra-chavan-state-president-of-maharashtra-bjp-who-says-bjp-is-my-identity-276739/amp/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://english.publictv.in/bjp-announces-new-state-chiefs-in-7-states-2-uts-moves-closer-to-elect-national-president/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/who-is-ravindra-chavan-ravindra-chavan-becomes-the-working-president-of-maharashtra-bjp-national-president-jp-nadda-announced-50716</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-mp-murlidhar-mohol-launches-citys-first-24x7-digital-citizen-service-office/</t>
+          <t>https://www.tarunbharat.com/ravindra-chavan-appointed-as-bjp-state-president/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/ex-minister-ravindra-chavan-files-nomination-for-maharashtra-bjp-chief-post-8800476</t>
+          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://tennews.in/ravindra-chavan-elected-unopposed-as-maha-bjp-chief/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-party-joining-key-congress-and-thackeray-shiv-sena-office-bearers-join-bjp-in-maharashtra-under-ravindra-chavan-s-leadership-1374978</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/who-is-ravindra-chavan-new-bjp-president-for-maharashtra-close-aide-of-cm-fadnavis-8810167</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavhan-to-become-12th-bjp-maharashtra-state-president-succeeding-a-long-line-of-leaders-in-party-s-45-year-history-1366862</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-to-appoints-ravindra-chavan-next-bjp-president-of-maharashtra-chandrashekhar-bawankule-amit-shah-visit-know-all/articleshow/121479121.cms</t>
+          <t>https://marathi.abplive.com/videos/news/politics-bjp-to-announce-ravindra-chavan-as-maharashtra-state-president-on-july-1-massive-party-gathering-planned-1366858</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/maharashtra-ravindra-chavan-set-to-become-new-president-of-state-bjp-said-sources-2025-06-30-1146038</t>
+          <t>https://marathi.abplive.com/videos/news/ravindra-chavan-unanimously-elected-maharashtra-bjp-president-faces-local-body-election-challenges-1367369</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/maharashtra-bjp-gets-new-president-ravindra-chavan-elected-unanimously-b628/</t>
+          <t>https://marathi.abplive.com/web-stories/politics/who-is-bharatiya-janata-party-state-president-of-maharashtra-ravindra-chavan-bjp-1367338</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-visited-sai-baba-in-shirdi-after-being-appointed-as-state-executive-president-of-bjp-maharashtra-marathi-news-1338130</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-big-announcement-from-bjp-amit-satam-elected-as-mumbai-city-president/articleshow/123494762.cms</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/hemant-khandelwal-will-be-the-new-president-of-madhya-pradesh-bjp-8808221</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-corona-update-rain-update-monsoon-ajchya-thalak-batmya-on-july-01-political-news-in-marathi-919652</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/maharashtra/who-is-maharashtra-bjp-new-president-ravindra-chavan-know-125070100083_1.html</t>
+          <t>https://www.tv9marathi.com/videos/ravindra-chavan-elected-bjp-maharashtra-president-1436164.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/ravindra-chavan-elected-unopposed-as-new-state-president-of-bharatiya-janata-party/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/sanjay-jagtap-joins-bjp-in-the-presence-of-bjp-state-president-ravindra-chavan/articleshow/122572770.cms</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-bjp-likely-to-contest-alone-amid-mumbai-bmc-polls-with-eknath-shinde-and-ajit-pawar-amit-shah-ravindra-chavan-meet/articleshow/122897869.cms</t>
+          <t>https://news.abplive.com/cities/ravindra-chavan-named-maharashtra-bjp-president-fadnavis-loyalist-savarkar-follower-who-is-ravindra-chavan-profile-1784513</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/kedar-jadhav-to-join-bjp-in-presence-maharashtra-cm-devendra-fadnavis-ravindra-chavan-mumbai-marathi-news-1353247</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/mumbai-receives-bodies-of-pahalgam-terror-attack-victims-134898349.html</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/ravindra-chavan-instructed-the-partys-office-bearers-in-western-maharashtra-pune-print-news-phm-00-5234205/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-convention-starts-in-shirdi-speculation-fumes-for-new-state-president-know-all/articleshow/117149931.cms</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/narendra-modis-government-has-lifted-25-crore-families-out-of-poverty-in-11-years-says-ravindra-chavan-in-press-conference-maharashtra-news-mhs25061203154</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/ravindra-jadeja-relation-with-bihar-journey-from-mahendra-singh-chauhan-to-dhoni/articleshow/121551590.cms</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-new-strength-in-bjp-organizational-building-appointments-of-963-mandal-presidents-completed-by-ravindra-chavan-marathi-news-1355302</t>
+          <t>https://www.indiatv.in/maharashtra/crew-member-roshni-songhare-died-in-air-india-plane-crash-in-ahmedabad-2025-06-12-1142268</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-news-sanjay-jagtap-joins-bjp-ravindra-chavan-s-presence-big-blow-to-congress-before-upcoming-elections-1370379</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/ahead-of-civic-polls-maharashtra-bjp-chief-stakes-claim-for-kdmc-mayors-post/articleshow/123077307.cms</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-maharashtra-annouces-50-district-president-navi-mumbai-rajesh-patil-mira-bhayandar-dilip-jain-check-full-list/articleshow/121136990.cms</t>
+          <t>https://www.ndtv.com/india-news/former-cricketer-kedar-jadhav-joins-bjp-8118085</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-maharashtra-bjp-president-likely-to-contest-mumbai-cricket-association-mca-election-in-november-after-delhi-visit-1374335</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ahead-of-local-body-polls-bjp-finalises-names-of-22-district-presidents/articleshow/121549544.cms</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/bjp-maharashtra-ravindra-chavan-set-to-be-elected-as-state-president-unopposed-formal-announcement-expected-tomorrow-1367175</t>
+          <t>https://www.msn.com/en-in/news/India/ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra/ar-AA1JFbMn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/editorial/will-ravindra-chavan-meet-the-challenge-of-the-bjp-state-president-in-marathi/898320/</t>
+          <t>https://www.bignewsnetwork.com/news/278530942/bjp-mla-amit-satam-announced-as-president-of-mumbai-unit-ahead-of-bmc-polls</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/ravindra-chavan-bjp-maharashtra-president/918909</t>
+          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/ravindra-chavan-state-president-of-maharashtra-bjp-who-says-bjp-is-my-identity-276739/amp/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bjp-strengthens-roots-in-vidarbha-313-mandals-formed-275-presidents-appointed/articleshow/120463852.cms</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/operation-eknath-shinde-had-a-big-responsibility-he-said-that-fadnavis-would-not-become-the-chief-minister-so-he-had-tears-in-his-eyes-story-told-by-ravindra-chavan-1369426</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bjp-to-get-new-nagpur-city-chief-ahead-of-local-body-polls/articleshow/120741284.cms</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/who-is-ravindra-chavan-ravindra-chavan-becomes-the-working-president-of-maharashtra-bjp-national-president-jp-nadda-announced-50716</t>
+          <t>https://www.punekarnews.in/pune-cm-fadnavis-inaugurates-mohols-24-7-public-office-hails-him-as-a-crisis-time-leader/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/ravindra-chavan-appointed-as-bjp-state-president/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/3/KDMC-Dr-Nanasaheb-Dharmadhikari-Pratishthan-Cleanliness-Campaign.html</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://marathi.hindustantimes.com/maharashtra/ravindra-chavan-elected-as-bjp-working-state-president-why-bjp-gave-responsibility-141736618335892.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
+          <t>https://www.hindustantimes.com/india-news/pune-bridge-collapse-new-bridge-sanctioned-a-year-ago-but-work-order-came-on-june-10-101750128084734.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-party-joining-key-congress-and-thackeray-shiv-sena-office-bearers-join-bjp-in-maharashtra-under-ravindra-chavan-s-leadership-1374978</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/centre-removes-turkish-firm-celebi-from-ground-handling-at-mumbai-airport/articleshow/122106708.cms</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavhan-to-become-12th-bjp-maharashtra-state-president-succeeding-a-long-line-of-leaders-in-party-s-45-year-history-1366862</t>
+          <t>https://indianexpress.com/article/cities/mumbai/rajendra-gavit-bjp-mla-second-marriage-hc-10086135/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-bjp-to-announce-ravindra-chavan-as-maharashtra-state-president-on-july-1-massive-party-gathering-planned-1366858</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/27/eknath-shinde-on-iconic-building-in-Mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/ravindra-chavan-unanimously-elected-maharashtra-bjp-president-faces-local-body-election-challenges-1367369</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-trilingual-policy-narendra-jadhav-committee-raj-thackeray-opposition-language-review-rm82</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/web-stories/politics/who-is-bharatiya-janata-party-state-president-of-maharashtra-ravindra-chavan-bjp-1367338</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/ravindra-chavan-elected-as-bjp-state-president/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.mumbaitak.in/political-news/story/story-of-kalyan-dombivli-why-are-conditions-of-kalyan-and-dombivali-cities-so-bad-despite-powerful-leaders-shrikant-shinde-ravindra-chavan-3197444-2025-08-21</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-big-announcement-from-bjp-amit-satam-elected-as-mumbai-city-president/articleshow/123494762.cms</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/25-03-2025-governor-radhakrishnan-cm-devendra-fadnavis-perform-bhumipujan-of-tribute-wall/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/who-is-ravindra-chavan-devendra-fadnavis-confidant-ravindra-chavan-elected-as-bjps-new-state-president-article-152194052</t>
+          <t>https://www.mymahanagar.com/editorial/will-ravindra-chavan-meet-the-challenge-of-the-bjp-state-president-in-marathi/898320/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-corona-update-rain-update-monsoon-ajchya-thalak-batmya-on-july-01-political-news-in-marathi-919652</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-assembly-monsoon-session-2025-live-updates-mahayuti-vs-mva-cm-devendra-fadnavis-8804189</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-june-maharashtra-assembly-monsoon-session-2025-of-the-legislature-begins-today-mahayuti-government-devendra-fadanvis-ajit-pawar-eknath-shinde-gkt-96-5192359/</t>
+          <t>https://indiagroundreport.com/mumbai-bjp-mla-amit-satam-becomes-mumbai-bjp-president/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/nashik-politics-shiv-sena-ubt-leader-sudhakar-badgujar-and-babanrao-gholap-join-bjp-party/articleshow/121908291.cms</t>
+          <t>https://www.ptinews.com/press-release/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy/2692193</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/sanjay-jagtap-joins-bjp-in-the-presence-of-bjp-state-president-ravindra-chavan/articleshow/122572770.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>https://news.abplive.com/cities/ravindra-chavan-named-maharashtra-bjp-president-fadnavis-loyalist-savarkar-follower-who-is-ravindra-chavan-profile-1784513</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/mumbai-receives-bodies-of-pahalgam-terror-attack-victims-134898349.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-convention-starts-in-shirdi-speculation-fumes-for-new-state-president-know-all/articleshow/117149931.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>https://www.aajtak.in/india/news/story/deadlock-between-bjp-high-command-and-rss-over-news-national-president-continues-ntc-rptc-2275062-2025-06-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/ravindra-jadeja-relation-with-bihar-journey-from-mahendra-singh-chauhan-to-dhoni/articleshow/121551590.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>https://www.indiatv.in/maharashtra/crew-member-roshni-songhare-died-in-air-india-plane-crash-in-ahmedabad-2025-06-12-1142268</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>https://www.nayaindia.com/news/bjp-presidents-of-three-states-decided/499890.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>https://www.aajtak.in/india/maharashtra/video/maharashtra-bjp-has-a-new-president-ravindra-chavan-has-become-the-state-head-ytvd-2277534-2025-07-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>https://www.ndtv.com/india-news/former-cricketer-kedar-jadhav-joins-bjp-8118085</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/ahead-of-civic-polls-maharashtra-bjp-chief-stakes-claim-for-kdmc-mayors-post/articleshow/123077307.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/en-in/news/India/3-term-mla-ameet-satam-named-bjp-mumbai-president-ahead-of-bmc-polls/ar-AA1L97Xi</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/07/29/bes35-mh-ex-minister-bjp.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>https://www.bignewsnetwork.com/news/278530942/bjp-mla-amit-satam-announced-as-president-of-mumbai-unit-ahead-of-bmc-polls</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/india-news/pune-bridge-collapse-new-bridge-sanctioned-a-year-ago-but-work-order-came-on-june-10-101750128084734.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/27/eknath-shinde-on-iconic-building-in-Mumbai.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-trilingual-policy-narendra-jadhav-committee-raj-thackeray-opposition-language-review-rm82</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>https://policenama.com/amit-satam-bjp-mumbai-amit-satam-appointed-as-mumbai-bjp-president-announcement-by-state-president-ravindra-chavan/</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-new-list-of-58-district-presidents-announced-in-the-state-with-mumbai-preparations-for-elections-devendra-fadnavis-chandrashekhar-bawankule-marathi-news-1358929</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/ravindra-chavan-elected-as-bjp-state-president/</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-assembly-monsoon-session-2025-live-updates-mahayuti-vs-mva-cm-devendra-fadnavis-8804189</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>https://indiagroundreport.com/mumbai-bjp-mla-amit-satam-becomes-mumbai-bjp-president/</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/press-release/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy/2692193</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
           <t>https://www.deccanherald.com/india/maharashtra/bjp-holds-meeting-of-former-mps-and-mlas-ahead-of-local-body-polls-in-maharashtra-3658754</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
         </is>
       </c>
     </row>

--- a/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A188"/>
+  <dimension ref="A1:A187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,21 +445,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ex-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president-3351330</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-names-ravindra-chavan-as-state-unit-chief-with-an-eye-on-mmr-101748631790329.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ravindra-chavan-set-to-head-maha-bjp-says-bawankule/articleshow/121504377.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ex-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president-3351330</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-names-ravindra-chavan-as-state-unit-chief-with-an-eye-on-mmr-101748631790329.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ravindra-chavan-set-to-head-maha-bjp-says-bawankule/articleshow/121504377.cms</t>
         </is>
       </c>
     </row>
@@ -536,14 +536,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/hindutva-not-against-any-religion-treating-all-religions-equally-is-true-secularism-nitin-gadkari-3611385</t>
+          <t>https://zeenews.india.com/india/who-is-ravindra-chavan-new-maharashtra-bjp-chief-close-confidant-of-cm-devendra-fadnavis-2925029.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/who-is-ravindra-chavan-new-maharashtra-bjp-chief-close-confidant-of-cm-devendra-fadnavis-2925029.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/hindutva-not-against-any-religion-treating-all-religions-equally-is-true-secularism-nitin-gadkari-3611385</t>
         </is>
       </c>
     </row>
@@ -557,70 +557,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/justice-chavan-calls-for-national-judicial-service-reforms-to-address-vacancies-in-judiciary/articleshow/121299899.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/viral-list-of-dist-chiefs-fake-bjp-warns-of-police-action/articleshow/121252533.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-files-nomination-for-post-of-maharashtra-bjp-president-23582507</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/justice-chavan-calls-for-national-judicial-service-reforms-to-address-vacancies-in-judiciary/articleshow/121299899.cms</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ex-minister-ravindra-chavan-is-bjp's-new-maharashtra-unit-chief/2690729</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-files-nomination-for-post-of-maharashtra-bjp-president-23582507</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/india-political-updates-latest-pm-narendra-modi-arvind-kejriwal-atishi-sanjay-singh-aap-bjp-congress-rahul-gandhi-delhi-assembly-elections-polls-live-politics-news-3350792</t>
+          <t>https://www.ptinews.com/story/national/ex-minister-ravindra-chavan-is-bjp's-new-maharashtra-unit-chief/2690729</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/amit-shah-to-begin-3-day-maharashtra-visit-ahead-of-local-body-polls-3556463</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/money-lender-booked-for-suicide-abetment-of-debtor/articleshow/121603123.cms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/ravindra-chavan-appointed-maharashtra-bjp-president/07021333</t>
+          <t>https://www.deccanherald.com/india/india-political-updates-latest-pm-narendra-modi-arvind-kejriwal-atishi-sanjay-singh-aap-bjp-congress-rahul-gandhi-delhi-assembly-elections-polls-live-politics-news-3350792</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/amit-shah-to-begin-3-day-maharashtra-visit-ahead-of-local-body-polls-3556463</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/58-bjp-chiefs-of-districts-named/articleshow/121146293.cms</t>
+          <t>https://www.nagpurtoday.in/ravindra-chavan-appointed-maharashtra-bjp-president/07021333</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-chief-in-maharashtra-brings-mns-union-workers-into-party/articleshow/123367896.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/58-bjp-chiefs-of-districts-named/articleshow/121146293.cms</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/ameet-satam-becomes-bjp-s-new-mumbai-chief-ahead-of-bmc-polls-who-is-he/ar-AA1L9t6x</t>
+          <t>https://www.aninews.in/news/national/politics/double-engine-govt-working-in-peoples-best-interests-new-maharashtra-bjp-chief-ravindra-chavan20250702021253</t>
         </is>
       </c>
     </row>
@@ -634,455 +634,455 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/dombivli-residents-demand-clarity-as-railways-issue-eviction-notices</t>
+          <t>https://tennews.in/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bjps-sankalp-to-siddhi-campaign-to-begin-this-week/articleshow/121606429.cms</t>
+          <t>https://thecsrjournal.in/indigos-agile-employees-secure-record-salary-hike-in-historic-agreement-with-union/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://tennews.in/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
+          <t>https://www.etvbharat.com/en/!state/bodies-of-pahalgam-terror-attack-victims-from-maharashtra-brought-to-mumbai-enn25042305870</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Pune-Congress-leader-Sanjay-Jagtap-joins-BJP/2733730</t>
+          <t>https://www.afternoonvoice.com/ravindra-chavan-a-visionary-leader-strengthening-maharashtra-bjps-political-landscape.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/indigos-agile-employees-secure-record-salary-hike-in-historic-agreement-with-union/</t>
+          <t>https://www.socialnews.xyz/?p=6725428</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6725428</t>
+          <t>https://gallinews.com/ravindra-chavan-bane-bjp-ke-naye-maharashtra-president/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://gallinews.com/ravindra-chavan-bane-bjp-ke-naye-maharashtra-president/</t>
+          <t>https://www.afternoonvoice.com/bjp-picks-ravindra-chavan-as-maharashtra-chief-ahead-of-key-civic-polls.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/bjp-picks-ravindra-chavan-as-maharashtra-chief-ahead-of-key-civic-polls.html</t>
+          <t>https://theindianawaaz.com/ravindra-chavan-appointed-as-bjp-state-president-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/ravindra-chavan-appointed-as-bjp-state-president-of-maharashtra/</t>
+          <t>https://www.cityairnews.com/content/ravindra-chavan-elected-unopposed-as-maha-bjp-chief</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.cityairnews.com/content/ravindra-chavan-elected-unopposed-as-maha-bjp-chief</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-appointed-ravindra-chavan-as-working-state-president-of-maharashtra-know-his-journey/articleshow/117154523.cms</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-kundmala-bridge-collapses-5-days-after-rs-8-crore-renovation-approval-sanjay-raut-alleges-corruption-claims-only-rs-80000-was-actually-sanctioned/</t>
+          <t>https://www.aajtak.in/topic/ravindra-chavan</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-local-election-bjp-president-ravindra-chavan-asked-former-mps-and-mlas-to-adopt-one-mandal-each-ann-2988472</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-chief-of-maharashtra-bjp-ravindra-chavan-name-is-almost-finalised-9348436.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-appointed-ravindra-chavan-as-working-state-president-of-maharashtra-know-his-journey/articleshow/117154523.cms</t>
+          <t>https://www.livehindustan.com/national/why-bjp-gave-responsibility-of-maharashtra-unit-to-ravindra-chavan-maratha-face-201736616683779.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/topic/ravindra-chavan</t>
+          <t>https://ndtv.in/india/ravindra-chavan-from-maharashtra-khandelwal-from-mp-became-new-state-president-of-bjp-know-all-details-here-8812249</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/why-bjp-gave-responsibility-of-maharashtra-unit-to-ravindra-chavan-maratha-face-201736616683779.html</t>
+          <t>https://www.jansatta.com/national/bjp-may-appoint-ravindra-chavan-maharashtra-state-president-cm-devendra-fadnavis/3775586/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-chief-of-maharashtra-bjp-ravindra-chavan-name-is-almost-finalised-9348436.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-why-party-appointed-know-all/articleshow/117210600.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-ravindra-chavan-can-become-president-of-maharashtra-bjp-mumbai-ann-2969682</t>
+          <t>https://ndtv.in/maharashtra-news/ravindra-chavan-new-maharashtra-bjp-president-know-his-political-journey-8811120</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/ravindra-chavan-from-maharashtra-khandelwal-from-mp-became-new-state-president-of-bjp-know-all-details-here-8812249</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-ravindra-chavan-warns-throw-away-the-list-of-81-district-presidents-of-bjp-don-t-make-it-viral-social-media-1359706</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/bjp-may-appoint-ravindra-chavan-maharashtra-state-president-cm-devendra-fadnavis/3775586/</t>
+          <t>https://www.lokmatnews.in/india/who-is-ravindra-chavan-bjp-mla-appointed-working-state-president-maharashtra-replace-chandrashekhar-bawankule-b507/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-why-party-appointed-know-all/articleshow/117210600.cms</t>
+          <t>https://marathi.ndtv.com/cities/kalyan-ex-bjp-mla-feud-viral-clip-shows-strong-words-against-kapil-patil-and-ravindra-chavan-in-heated-exchange-9007785</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-name-suggested-as-maharashtra-bjp-president-by-chandrashekhar-bawankule-2971280</t>
+          <t>https://mandalnews.com/maharashtra/ravindra-chauhan-on-the-post-of-bjp-maharashtra-state-president/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/ravindra-chavan-new-maharashtra-bjp-president-know-his-political-journey-8811120</t>
+          <t>https://marathi.ndtv.com/cities/bjp-news-ravindra-chavan-appointed-bjps-maharashtra-working-president-7451905</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-ravindra-chavan-warns-throw-away-the-list-of-81-district-presidents-of-bjp-don-t-make-it-viral-social-media-1359706</t>
+          <t>https://marathi.ndtv.com/politics/bjp-state-president-ravindra-chavan-makes-big-statement-on-alliance-with-uddhav-thackeray-8864806</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/who-is-ravindra-chavan-bjp-mla-appointed-working-state-president-maharashtra-replace-chandrashekhar-bawankule-b507/</t>
+          <t>https://marathi.ndtv.com/politics/ravindra-chavan-opens-up-about-disappointment-over-eknath-shinde-becoming-chief-minister-reveals-true-feelings-8865262</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/kalyan-ex-bjp-mla-feud-viral-clip-shows-strong-words-against-kapil-patil-and-ravindra-chavan-in-heated-exchange-9007785</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-brahmin-obc-maratha-formula-ravindra-chouhan-chandrashekhar-bawankule-8954968.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/maharashtra/ravindra-chauhan-on-the-post-of-bjp-maharashtra-state-president/</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-elected-as-bjp-working-state-president-maharashtra-politics-marathi-news-1338059</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/bjp-news-ravindra-chavan-appointed-bjps-maharashtra-working-president-7451905</t>
+          <t>https://marathi.ndtv.com/politics/bjp-state-working-president-ravindra-chavan-responds-congress-state-president-harshvardhan-sapkal-8802075</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/bjp-state-president-ravindra-chavan-makes-big-statement-on-alliance-with-uddhav-thackeray-8864806</t>
+          <t>https://www.tv9marathi.com/videos/ravindra-chavan-appointed-maharashtra-bjp-president-1436968.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/ravindra-chavan-opens-up-about-disappointment-over-eknath-shinde-becoming-chief-minister-reveals-true-feelings-8865262</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-politics-bjp-leader-ravindra-chavan-unanimously-elected-maharashtra-bjp-president-80826</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/maharashtra-council-established-for-1-5-lakh-marathi-speakers/</t>
+          <t>https://www.localnewsnetwork.in/mla-ravindra-chavan-has-been-appointed-as-the-maharashtra-state-executive-president-of-bjp/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-brahmin-obc-maratha-formula-ravindra-chouhan-chandrashekhar-bawankule-8954968.html</t>
+          <t>https://marathi.abplive.com/news/nanded/congress-mp-ravindra-chavan-warning-to-follow-protocol-due-to-nanded-municipal-corporation-commissioner-over-not-inviting-for-programme-1360903</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-elected-as-bjp-working-state-president-maharashtra-politics-marathi-news-1338059</t>
+          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-appointed-as-bjp-state-working-president-by-j-p-nadda/articleshow/117154533.cms</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/bjp-state-working-president-ravindra-chavan-responds-congress-state-president-harshvardhan-sapkal-8802075</t>
+          <t>https://news18marathi.com/maharashtra/ravindra-chavan-to-be-new-maharashtra-bjp-president-show-of-power-at-aaditya-thackeray-constituency-1425668.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-politics-bjp-leader-ravindra-chavan-unanimously-elected-maharashtra-bjp-president-80826</t>
+          <t>https://www.msn.com/mr-in/news/other/bjp-ravindra-chavan-news-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%9F-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-maharashtra-politics/vi-AA1K12wX</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-appointed-as-bjp-state-working-president-by-j-p-nadda/articleshow/117154533.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/30/from-party-worker-to-state-president.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/ravindra-chavan-to-be-new-maharashtra-bjp-president-show-of-power-at-aaditya-thackeray-constituency-1425668.html</t>
+          <t>https://marathi.ndtv.com/politics/mahayuti-news-unveiling-of-chhatrapati-shivaji-maharaj-statue-in-dombivli-shiv-sena-shinde-faction-criticizes-bjp-mla-ravindra-chavan-7945018</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/bjp-ravindra-chavan-news-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%9F-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-maharashtra-politics/vi-AA1K12wX</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/3/the-theme-of-the-dombivalikar-friendship-run-was-unveiled-by-bjp-state-president-ravindra-chavan.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/new-bjp-maharashtra-state-president-ravindra-chavan-political-journey-complete-information-marathi-916730.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bjp-leadership-meet-ravindra-chavan-meets-jp-nadda-in-delhi-first-meeting-as-state-president-earlier-met-amit-shah-in-pune-1368594</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/3/the-theme-of-the-dombivalikar-friendship-run-was-unveiled-by-bjp-state-president-ravindra-chavan.html</t>
+          <t>https://deshdoot.com/maharashtra-bjp-news-ravindra-chavan-appointed-as-bjp-state-president/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/30/from-party-worker-to-state-president.html</t>
+          <t>https://deshdoot.com/maharashtra-bjp-news-former-minister-ravindra-chavan-files-application-for-bjp-state-president-post/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/mahayuti-news-unveiling-of-chhatrapati-shivaji-maharaj-statue-in-dombivli-shiv-sena-shinde-faction-criticizes-bjp-mla-ravindra-chavan-7945018</t>
+          <t>https://marathi.abplive.com/tv-show/majha-vishesh/maharashtra-bjp-president-ravindra-chavan-s-first-interview-reveals-role-in-operation-shinde-discusses-mahayuti-election-strategy-it-notices-and-marathi-politics-1369435</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bjp-leadership-meet-ravindra-chavan-meets-jp-nadda-in-delhi-first-meeting-as-state-president-earlier-met-amit-shah-in-pune-1368594</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-and-local-body-polls/articleshow/122185894.cms</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/not-a-single-resident-of-65-buildings-in-kalyan-dombivli-will-be-allowed-to-become-homeless-assures-ravindra-chavan-817558.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/ravindra-chavan-says-thanks-to-his-party-after-selected-for-bjp-maharashtra-president/articleshow/122185577.cms</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/bjp-needs-a-mayor-to-remove-the-development-eclipse-of-kalyan-dombivali-bjp-state-president-ravindra-chavan/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/31/adopt-one-mandal-each-and-resolve-to-build-an-organization-state-president-ravindra-chavan-appeals-to-former-m.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/regarding-the-stalled-redevelopment-case-of-shantidoot-housing-society-and-lig-1-buildings-in-kalyan-956786.html</t>
+          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-may-be-elected-as-bjp-state-president-for-maharashtra-marathi-news/articleshow/122124651.cms</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/tv-show/majha-vishesh/maharashtra-bjp-president-ravindra-chavan-s-first-interview-reveals-role-in-operation-shinde-discusses-mahayuti-election-strategy-it-notices-and-marathi-politics-1369435</t>
+          <t>https://deshdoot.com/bjp-state-president-ravindra-chavan-good-luck-minister-vikhe-patil-rahata/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-and-local-body-polls/articleshow/122185894.cms</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-amit-satam-elected-as-mumbai-president-of-bjp-cm-devendra-fadnavis-9153593</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/ravindra-chavan-says-thanks-to-his-party-after-selected-for-bjp-maharashtra-president/articleshow/122185577.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-bjp-calls-urgent-meeting-in-mumbai-raj-thackeray-takes-aggressive-stance-on-matak-sodi-allegations-1379525</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/31/adopt-one-mandal-each-and-resolve-to-build-an-organization-state-president-ravindra-chavan-appeals-to-former-m.html</t>
+          <t>https://marathi.indiatimes.com/photogallery/news/ravindra-chavan-important-role-when-eknath-shinde-takeover-shiv-sena/photoshow/122188079.cms</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-exclusive-interview-talk-about-will-there-be-challenge-to-bjp-if-raj-thackeray-uddhav-thackeray-come-together-maharashtra-politics-marathi-news-1369421</t>
+          <t>https://www.mymahanagar.com/mahamumbai/bjp-live-devendra-fadnavis-annasaheb-dange-join-bjp-30th-july-ravindra-chavan-chardrakant-patil/907022/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/ravindra-chavan-political-masterstroke-ulhasnagar-sharad-pawar-group-breakdown-1445668.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/big-changes-underway-in-bjp-kdmc-ahead-of-municipal-elections/articleshow/121160143.cms</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/bjp-leader-ravindra-chavan-express-feeelings-after-become-a-bjp-maharashtra-president-916809.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-politics-1500-members-of-uddhav-thackerays-party-join-bjp-party-entry-in-mumbai-in-the-presence-of-ravindra-chavan/910127</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/congress-leader-kailash-gorantyal-and-suresh-varpudkar-will-join-bjp-under-the-leadership-of-state-president-ravindra-chavan-at-mumbai-jalna-constituency-before-election-1373052</t>
+          <t>https://www.mymahanagar.com/mahamumbai/dahi-handi-2025-dahi-handi-celebrated-in-a-traditional-manner-in-dombivli-bjp-mla-ravindra-chavan/912575/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-may-be-elected-as-bjp-state-president-for-maharashtra-marathi-news/articleshow/122124651.cms</t>
+          <t>https://marathi.abplive.com/news/politics/sudhakar-badgujar-bjp-chandrashekhar-bawankule-he-join-bjp-with-girish-mahajan-and-ravindra-chavan-1364736</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-amit-satam-elected-as-mumbai-president-of-bjp-cm-devendra-fadnavis-9153593</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nanded/set-back-for-bjp-ashok-chavan-discussion-on-alliance-between-congress-and-prakash-ambedkar-vanchit-bahujan-aghadi/articleshow/122873066.cms</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-bjp-calls-urgent-meeting-in-mumbai-raj-thackeray-takes-aggressive-stance-on-matak-sodi-allegations-1379525</t>
+          <t>https://marathi.abplive.com/news/nanded/nanded-news-congress-and-vanchit-hint-at-alliance-for-local-government-elections-in-nanded-will-consider-proposal-if-received-1371522</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-politics-1500-members-of-uddhav-thackerays-party-join-bjp-party-entry-in-mumbai-in-the-presence-of-ravindra-chavan/910127</t>
+          <t>https://news18marathi.com/maharashtra/bjp-leader-vikas-mhatre-resigns-from-bjp-ahead-dombivli-mahapalika-election-allegation-on-ravindra-chavan-1423215.html</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/dahi-handi-2025-dahi-handi-celebrated-in-a-traditional-manner-in-dombivli-bjp-mla-ravindra-chavan/912575/</t>
+          <t>https://www.etvbharat.com/mr/!state/dhule-congress-leader-kunal-patil-dismisses-rumors-of-joining-bjp-maharashtra-news-mhs25062501797</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nanded/set-back-for-bjp-ashok-chavan-discussion-on-alliance-between-congress-and-prakash-ambedkar-vanchit-bahujan-aghadi/articleshow/122873066.cms</t>
+          <t>https://www.tarunbharat.com/youth-leader-vishal-parab-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/nanded-news-congress-and-vanchit-hint-at-alliance-for-local-government-elections-in-nanded-will-consider-proposal-if-received-1371522</t>
+          <t>https://www.etvbharat.com/mr/!state/shetkari-kamgar-paksha-skp-jayant-patils-brother-pandit-patil-to-join-bjp-mumbai-maharashtra-maharashtra-news-mhs25041603477</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/youth-leader-vishal-parab-joins-bjp/</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-misssion-mumbai-bjp-will-turn-the-tables-meeting-for-the-post-of-mumbai-president-on-place-of-ashish-shelar-two-mlas-put-forward-their-names-pravin-darekar-1354321</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/congress-may-alliance-with-vba-party-in-nanded-for-upcoming-municipal-election-942211.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/raigad/shivsena-mla-mahendra-thorve-join-bjp-in-raigad-before-local-government-elections-marathi-news/articleshow/121927356.cms</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/shetkari-kamgar-paksha-skp-jayant-patils-brother-pandit-patil-to-join-bjp-mumbai-maharashtra-maharashtra-news-mhs25041603477</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/former-congress-mla-kailash-gorantyal-joins-bjp-major-challenge-for-shinde-led-shiv-sena-in-jalna/articleshow/123019959.cms</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/raigad/shivsena-mla-mahendra-thorve-join-bjp-in-raigad-before-local-government-elections-marathi-news/articleshow/121927356.cms</t>
+          <t>https://marathi.indiatimes.com/photogallery/news/congress-leader-kunal-patil-may-be-join-bjp-soon/photoshow/122030946.cms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/former-congress-mla-kailash-gorantyal-joins-bjp-major-challenge-for-shinde-led-shiv-sena-in-jalna/articleshow/123019959.cms</t>
+          <t>https://www.newsnationtv.com/--20250502182005/</t>
         </is>
       </c>
     </row>
@@ -1096,21 +1096,21 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/maharashtra/ravindra-chavan-new-bjp-maharashtra-president/articleshow-x7qax8g</t>
+          <t>https://www.dainikprabhat.com/bjp-will-get-a-new-state-president-today-ravindra-chavan-will-accept-the-oath/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/bjp-will-get-a-new-state-president-today-ravindra-chavan-will-accept-the-oath/</t>
+          <t>https://civicmirror.in/maharashtra/four-former-corporators-of-ubatha-in-malvan-join-bjp-along-with-their-supporters/cid1752483678.htm</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/four-former-corporators-of-ubatha-in-malvan-join-bjp-along-with-their-supporters/cid1752483678.htm</t>
+          <t>https://www.marathiebatmya.com/political/bhor-mulshi-taluka-workers-from-various-parties-join-bjp/</t>
         </is>
       </c>
     </row>
@@ -1159,28 +1159,28 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/the-election-of-bjp-state-president-will-be-held-on-july-1-and-ravindra-chavan-is-likely-to-be-the-candidate/897175/</t>
+          <t>https://news18marathi.com/mumbai/ravindra-chavan-has-become-the-new-bjp-maharashtra-president-1426306.html</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/mumbai/ravindra-chavan-has-become-the-new-bjp-maharashtra-president-1426306.html</t>
+          <t>https://www.mymahanagar.com/photo-gallery/ravindra-chavan-appealed-to-the-workers-after-assuming-the-post-of-bjp-state-president/898007/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/photo-gallery/ravindra-chavan-appealed-to-the-workers-after-assuming-the-post-of-bjp-state-president/898007/</t>
+          <t>https://marathi.abplive.com/videos/news/politics-bjp-maharashtra-state-president-election-nomination-process-begins-ravindra-chavhan-likely-to-secure-position-1367011</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-bjp-maharashtra-state-president-election-nomination-process-begins-ravindra-chavhan-likely-to-secure-position-1367011</t>
+          <t>https://www.etvbharat.com/mr/!state/four-former-corporators-of-ubt-in-malvan-join-bjp-along-with-their-supporters-welcomed-by-bjp-state-president-ravindra-chavan-maharashtra-news-mhs25071403115</t>
         </is>
       </c>
     </row>
@@ -1201,42 +1201,42 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/bhor-mulshi-taluka-workers-from-various-parties-join-bjp/</t>
+          <t>https://www.msn.com/en-gb/news/world/kedar-jadhav-makes-bold-prediction-about-india-playing-pakistan-in-asia-cup/ar-AA1KJnU4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-gb/news/world/kedar-jadhav-makes-bold-prediction-about-india-playing-pakistan-in-asia-cup/ar-AA1KJnU4</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/4-ex-congress-corporators-join-bjp-in-kalyan-dombivli/articleshow/123447826.cms</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/4-ex-congress-corporators-join-bjp-in-kalyan-dombivli/articleshow/123447826.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-inducts-key-pwp-leaders-before-local-body-elections-101744831159344.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-inducts-key-pwp-leaders-before-local-body-elections-101744831159344.html</t>
+          <t>https://www.livemint.com/politics/news/no-one-becomes-great-by-imposing-themselves-nitin-gadkari-warns-against-arrogance-in-leadership-cong-reacts-11752387796290.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/politics/news/no-one-becomes-great-by-imposing-themselves-nitin-gadkari-warns-against-arrogance-in-leadership-cong-reacts-11752387796290.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
         </is>
       </c>
     </row>
@@ -1250,63 +1250,63 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/ncp-shiv-sena-ubt-members-join-bjp-in-nashik/articleshow/122233115.cms</t>
+          <t>https://www.ptinews.com/editor-detail/Pune-Congress-leader-Sanjay-Jagtap-joins-BJP/2733730</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/congress-ex-mla-suresh-warpudkar-and-family-set-to-join-bjp/articleshow/122951927.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/ncp-shiv-sena-ubt-members-join-bjp-in-nashik/articleshow/122233115.cms</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/bjp-state-chiefs-kharges-high-command-remark-congress-bihar-elections-modi-sonia-rahul-gandhi-socialist-secular-rss-constitution-india-tamil-nadu-3610086</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/congress-ex-mla-suresh-warpudkar-and-family-set-to-join-bjp/articleshow/122951927.cms</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/emotional-farewell-outgoing-bjp-state-president-bawankule-pens-heartfelt-letter-to-party-workers/07021355</t>
+          <t>https://www.deccanherald.com/india/bjp-state-chiefs-kharges-high-command-remark-congress-bihar-elections-modi-sonia-rahul-gandhi-socialist-secular-rss-constitution-india-tamil-nadu-3610086</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/ravindra-chavan-a-visionary-leader-strengthening-maharashtra-bjps-political-landscape.html</t>
+          <t>https://www.nagpurtoday.in/emotional-farewell-outgoing-bjp-state-president-bawankule-pens-heartfelt-letter-to-party-workers/07021355</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/congress-receives-a-jolt-after-former-dhule-mla-kunal-patil-joins-bjp/</t>
+          <t>https://www.bhaskarenglish.in/national/news/bjp-state-presidents-appointment-national-president-election-july-maharashtra-himachal-pm-modi-jp-nadda-135348404.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/bjp-state-presidents-appointment-national-president-election-july-maharashtra-himachal-pm-modi-jp-nadda-135348404.html</t>
+          <t>https://english.publictv.in/bjp-announces-new-state-chiefs-in-7-states-2-uts-moves-closer-to-elect-national-president/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://english.publictv.in/bjp-announces-new-state-chiefs-in-7-states-2-uts-moves-closer-to-elect-national-president/</t>
+          <t>https://www.mypunepulse.com/pune-mp-murlidhar-mohol-launches-citys-first-24x7-digital-citizen-service-office/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/who-is-the-new-bjp-party-president-list-of-state-party-president-out-11032/</t>
+          <t>https://kknlive.com/en/andhra-pradesh-en/bjp-appoints-new-state-presidents-in-9-states/</t>
         </is>
       </c>
     </row>
@@ -1334,42 +1334,42 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/double-engine-govt-working-in-peoples-best-interests-new-maharashtra-bjp-chief-ravindra-chavan20250702021253/</t>
+          <t>https://tennews.in/ravindra-chavan-elected-unopposed-as-maha-bjp-chief/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://tennews.in/ravindra-chavan-elected-unopposed-as-maha-bjp-chief/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/andheri-mla-ameet-satam-to-lead-mumbai-unit-as-party-gears-up-for-high-stakes-bmc-battle-23591113</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy/</t>
+          <t>https://ndtv.in/india/who-is-ravindra-chavan-new-bjp-president-for-maharashtra-close-aide-of-cm-fadnavis-8810167</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/who-is-ravindra-chavan-new-bjp-president-for-maharashtra-close-aide-of-cm-fadnavis-8810167</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-to-appoints-ravindra-chavan-next-bjp-president-of-maharashtra-chandrashekhar-bawankule-amit-shah-visit-know-all/articleshow/121479121.cms</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-to-appoints-ravindra-chavan-next-bjp-president-of-maharashtra-chandrashekhar-bawankule-amit-shah-visit-know-all/articleshow/121479121.cms</t>
+          <t>https://www.indiatv.in/maharashtra/maharashtra-ravindra-chavan-set-to-become-new-president-of-state-bjp-said-sources-2025-06-30-1146038</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/maharashtra-ravindra-chavan-set-to-become-new-president-of-state-bjp-said-sources-2025-06-30-1146038</t>
+          <t>https://www.livemint.com/hindi/trends/maharashtra-bjp-gets-new-state-chief-heres-all-about-newly-appointed-party-president-ravindra-chavan-know-who-is-he-241751382375965.html</t>
         </is>
       </c>
     </row>
@@ -1383,98 +1383,98 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/ravindra-chavan-elected-unopposed-as-new-state-president-of-bharatiya-janata-party/</t>
+          <t>https://ndtv.in/india/hemant-khandelwal-will-be-the-new-president-of-madhya-pradesh-bjp-8808221</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/maharashtra/who-is-maharashtra-bjp-new-president-ravindra-chavan-know-125070100083_1.html</t>
+          <t>https://www.newsonair.gov.in/mr/ravindra-chavan-elected-unopposed-as-new-state-president-of-bharatiya-janata-party/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/hemant-khandelwal-will-be-the-new-president-of-madhya-pradesh-bjp-8808221</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-bjp-likely-to-contest-alone-amid-mumbai-bmc-polls-with-eknath-shinde-and-ajit-pawar-amit-shah-ravindra-chavan-meet/articleshow/122897869.cms</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-bjp-likely-to-contest-alone-amid-mumbai-bmc-polls-with-eknath-shinde-and-ajit-pawar-amit-shah-ravindra-chavan-meet/articleshow/122897869.cms</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-new-strength-in-bjp-organizational-building-appointments-of-963-mandal-presidents-completed-by-ravindra-chavan-marathi-news-1355302</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/bjp-announces-new-state-presidents-in-4-states-changes-in-maharashtra-uttarakhand-telangana-and-himachal-pradesh/articleshow/122163940.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-maharashtra-annouces-50-district-president-navi-mumbai-rajesh-patil-mira-bhayandar-dilip-jain-check-full-list/articleshow/121136990.cms</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-news-sanjay-jagtap-joins-bjp-ravindra-chavan-s-presence-big-blow-to-congress-before-upcoming-elections-1370379</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-maharashtra-bjp-president-likely-to-contest-mumbai-cricket-association-mca-election-in-november-after-delhi-visit-1374335</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-maharashtra-annouces-50-district-president-navi-mumbai-rajesh-patil-mira-bhayandar-dilip-jain-check-full-list/articleshow/121136990.cms</t>
+          <t>https://marathi.abplive.com/videos/news/bjp-maharashtra-ravindra-chavan-set-to-be-elected-as-state-president-unopposed-formal-announcement-expected-tomorrow-1367175</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/parbhani-congress-leader-suresh-warpudkar-joins-bjp-with-supporters-ahead-of-nagar-nikay-chunav-2987557</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-bjp-party-maharashtra-state-president-after-sthanik-swarajya-sanstha-election-chandrashekhar-bawankule-maharashtra-news-12-jan-2025-abp-majha-1338092</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/bjp-maharashtra-ravindra-chavan-set-to-be-elected-as-state-president-unopposed-formal-announcement-expected-tomorrow-1367175</t>
+          <t>https://www.mymahanagar.com/editorial/will-ravindra-chavan-meet-the-challenge-of-the-bjp-state-president-in-marathi/898320/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-maharashtra-bjp-president-likely-to-contest-mumbai-cricket-association-mca-election-in-november-after-delhi-visit-1374335</t>
+          <t>https://www.tv9marathi.com/videos/ravindra-chavan-elected-bjp-maharashtra-president-1436164.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/ravindra-chavan-state-president-of-maharashtra-bjp-who-says-bjp-is-my-identity-276739/amp/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-state-president-ravindra-chavan-held-meeting-former-mps-mlas-for-preparation-upcoming-local-body-elections/articleshow/123032835.cms</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/who-is-ravindra-chavan-ravindra-chavan-becomes-the-working-president-of-maharashtra-bjp-national-president-jp-nadda-announced-50716</t>
+          <t>https://thefocusindia.com/maharashtra-news/ravindra-chavan-state-president-of-maharashtra-bjp-who-says-bjp-is-my-identity-276739/amp/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/ravindra-chavan-appointed-as-bjp-state-president/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/who-is-ravindra-chavan-ravindra-chavan-becomes-the-working-president-of-maharashtra-bjp-national-president-jp-nadda-announced-50716</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
+          <t>https://www.tarunbharat.com/ravindra-chavan-appointed-as-bjp-state-president/</t>
         </is>
       </c>
     </row>
@@ -1488,231 +1488,231 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavhan-to-become-12th-bjp-maharashtra-state-president-succeeding-a-long-line-of-leaders-in-party-s-45-year-history-1366862</t>
+          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-bjp-to-announce-ravindra-chavan-as-maharashtra-state-president-on-july-1-massive-party-gathering-planned-1366858</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavhan-to-become-12th-bjp-maharashtra-state-president-succeeding-a-long-line-of-leaders-in-party-s-45-year-history-1366862</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/ravindra-chavan-unanimously-elected-maharashtra-bjp-president-faces-local-body-election-challenges-1367369</t>
+          <t>https://marathi.abplive.com/videos/news/politics-bjp-to-announce-ravindra-chavan-as-maharashtra-state-president-on-july-1-massive-party-gathering-planned-1366858</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/web-stories/politics/who-is-bharatiya-janata-party-state-president-of-maharashtra-ravindra-chavan-bjp-1367338</t>
+          <t>https://marathi.abplive.com/videos/news/ravindra-chavan-unanimously-elected-maharashtra-bjp-president-faces-local-body-election-challenges-1367369</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-big-announcement-from-bjp-amit-satam-elected-as-mumbai-city-president/articleshow/123494762.cms</t>
+          <t>https://www.tv9marathi.com/videos/bjp-ravindra-chavan-on-thackeray-brothers-alliance-mahayuti-bmc-election-strategy-hindi-marathi-controversy-1444066.html</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-corona-update-rain-update-monsoon-ajchya-thalak-batmya-on-july-01-political-news-in-marathi-919652</t>
+          <t>https://marathi.abplive.com/web-stories/politics/who-is-bharatiya-janata-party-state-president-of-maharashtra-ravindra-chavan-bjp-1367338</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ravindra-chavan-elected-bjp-maharashtra-president-1436164.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-big-announcement-from-bjp-amit-satam-elected-as-mumbai-city-president/articleshow/123494762.cms</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/sanjay-jagtap-joins-bjp-in-the-presence-of-bjp-state-president-ravindra-chavan/articleshow/122572770.cms</t>
+          <t>https://marathi.timesnownews.com/maharashtra/who-is-ravindra-chavan-devendra-fadnavis-confidant-ravindra-chavan-elected-as-bjps-new-state-president-article-152194052</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/ravindra-chavan-named-maharashtra-bjp-president-fadnavis-loyalist-savarkar-follower-who-is-ravindra-chavan-profile-1784513</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-corona-update-rain-update-monsoon-ajchya-thalak-batmya-on-july-01-political-news-in-marathi-919652</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/mumbai-receives-bodies-of-pahalgam-terror-attack-victims-134898349.html</t>
+          <t>https://news.abplive.com/cities/ravindra-chavan-named-maharashtra-bjp-president-fadnavis-loyalist-savarkar-follower-who-is-ravindra-chavan-profile-1784513</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-convention-starts-in-shirdi-speculation-fumes-for-new-state-president-know-all/articleshow/117149931.cms</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/mumbai-receives-bodies-of-pahalgam-terror-attack-victims-134898349.html</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/ravindra-jadeja-relation-with-bihar-journey-from-mahendra-singh-chauhan-to-dhoni/articleshow/121551590.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-convention-starts-in-shirdi-speculation-fumes-for-new-state-president-know-all/articleshow/117149931.cms</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/crew-member-roshni-songhare-died-in-air-india-plane-crash-in-ahmedabad-2025-06-12-1142268</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/ravindra-jadeja-relation-with-bihar-journey-from-mahendra-singh-chauhan-to-dhoni/articleshow/121551590.cms</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/ahead-of-civic-polls-maharashtra-bjp-chief-stakes-claim-for-kdmc-mayors-post/articleshow/123077307.cms</t>
+          <t>https://www.indiatv.in/maharashtra/crew-member-roshni-songhare-died-in-air-india-plane-crash-in-ahmedabad-2025-06-12-1142268</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/former-cricketer-kedar-jadhav-joins-bjp-8118085</t>
+          <t>https://www.nayaindia.com/news/bjp-presidents-of-three-states-decided/499890.html</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ahead-of-local-body-polls-bjp-finalises-names-of-22-district-presidents/articleshow/121549544.cms</t>
+          <t>https://globalgreenews.com/2025/07/02/maharashtra-bjp-leader-ravindra-chavan-appointed-as-new-state-president/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra/ar-AA1JFbMn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ndtv.com/india-news/former-cricketer-kedar-jadhav-joins-bjp-8118085</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278530942/bjp-mla-amit-satam-announced-as-president-of-mumbai-unit-ahead-of-bmc-polls</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-chief-in-maharashtra-brings-mns-union-workers-into-party/articleshow/123367896.cms</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/ahead-of-civic-polls-maharashtra-bjp-chief-stakes-claim-for-kdmc-mayors-post/articleshow/123077307.cms</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bjp-strengthens-roots-in-vidarbha-313-mandals-formed-275-presidents-appointed/articleshow/120463852.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ahead-of-local-body-polls-bjp-finalises-names-of-22-district-presidents/articleshow/121549544.cms</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bjp-to-get-new-nagpur-city-chief-ahead-of-local-body-polls/articleshow/120741284.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra-23587437</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-cm-fadnavis-inaugurates-mohols-24-7-public-office-hails-him-as-a-crisis-time-leader/</t>
+          <t>https://www.msn.com/en-in/news/India/ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra/ar-AA1JFbMn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/3/KDMC-Dr-Nanasaheb-Dharmadhikari-Pratishthan-Cleanliness-Campaign.html</t>
+          <t>https://www.bignewsnetwork.com/news/278530942/bjp-mla-amit-satam-announced-as-president-of-mumbai-unit-ahead-of-bmc-polls</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
+          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/pune-bridge-collapse-new-bridge-sanctioned-a-year-ago-but-work-order-came-on-june-10-101750128084734.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/3/KDMC-Dr-Nanasaheb-Dharmadhikari-Pratishthan-Cleanliness-Campaign.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/centre-removes-turkish-firm-celebi-from-ground-handling-at-mumbai-airport/articleshow/122106708.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/rajendra-gavit-bjp-mla-second-marriage-hc-10086135/</t>
+          <t>https://www.hindustantimes.com/india-news/pune-bridge-collapse-new-bridge-sanctioned-a-year-ago-but-work-order-came-on-june-10-101750128084734.html</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/27/eknath-shinde-on-iconic-building-in-Mumbai.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/centre-removes-turkish-firm-celebi-from-ground-handling-at-mumbai-airport/articleshow/122106708.cms</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-trilingual-policy-narendra-jadhav-committee-raj-thackeray-opposition-language-review-rm82</t>
+          <t>https://indianexpress.com/article/cities/mumbai/rajendra-gavit-bjp-mla-second-marriage-hc-10086135/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/ravindra-chavan-elected-as-bjp-state-president/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/27/eknath-shinde-on-iconic-building-in-Mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-trilingual-policy-narendra-jadhav-committee-raj-thackeray-opposition-language-review-rm82</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/25-03-2025-governor-radhakrishnan-cm-devendra-fadnavis-perform-bhumipujan-of-tribute-wall/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/ravindra-chavan-elected-as-bjp-state-president/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/editorial/will-ravindra-chavan-meet-the-challenge-of-the-bjp-state-president-in-marathi/898320/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
@@ -1732,13 +1732,6 @@
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/press-release/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy/2692193</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
         <is>
           <t>https://www.deccanherald.com/india/maharashtra/bjp-holds-meeting-of-former-mps-and-mlas-ahead-of-local-body-polls-in-maharashtra-3658754</t>
         </is>

--- a/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A187"/>
+  <dimension ref="A1:A197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,35 +445,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-names-ravindra-chavan-as-state-unit-chief-with-an-eye-on-mmr-101748631790329.html</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/bjp-mayor-needed-to-remove-the-stagnation-in-kalyan-dombivlis-development-says-bjp-maharashtra-president-ravindra-chavan/articleshow/123073337.cms</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ex-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president-3351330</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-names-ravindra-chavan-as-state-unit-chief-with-an-eye-on-mmr-101748631790329.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ravindra-chavan-set-to-head-maha-bjp-says-bawankule/articleshow/121504377.cms</t>
+          <t>https://www.ndtv.com/india-news/hemant-khandelwal-ravindra-chavan-pvn-madhav-n-ramchander-rao-a-look-at-9-new-bjp-state-chiefs-before-jp-naddas-replacement-polls-8812562</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/bjp-mayor-needed-to-remove-the-stagnation-in-kalyan-dombivlis-development-says-bjp-maharashtra-president-ravindra-chavan/articleshow/123073337.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ex-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president-3351330</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/hemant-khandelwal-ravindra-chavan-pvn-madhav-n-ramchander-rao-a-look-at-9-new-bjp-state-chiefs-before-jp-naddas-replacement-polls-8812562</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ravindra-chavan-set-to-head-maha-bjp-says-bawankule/articleshow/121504377.cms</t>
         </is>
       </c>
     </row>
@@ -487,1251 +487,1321 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-polls-2025-07-01-996989</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/dombivli-pride-2025-grand-dahi-handi-celebrates-janmashtami-bjp-leader-ravindra-chavan-urges-youth-to-drive-maharashtras-growth/articleshow/123332580.cms</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/dombivli-pride-2025-grand-dahi-handi-celebrates-janmashtami-bjp-leader-ravindra-chavan-urges-youth-to-drive-maharashtras-growth/articleshow/123332580.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ravindra-chavan-set-to-be-bjp-state-president-101751310615190.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ravindra-chavan-set-to-be-bjp-state-president-101751310615190.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ravindra-chavan-to-be-new-bjp-chief-for-maharashtra-3609432</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ravindra-chavan-to-be-new-bjp-chief-for-maharashtra-3609432</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-unanimously-elected-as-new-maharashtra-bjp-president-23582746</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/meeting-with-ravindra-chavan-personal-not-political-maharashtra-congress-leader-kunal-patil-dismisses-bjp-switch-rumours-enn25062503849</t>
+          <t>https://www.financialexpress.com/india-news/who-is-ravindra-chavan-four-time-mla-appointed-as-maharashtra-units-new-president/3899457/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-unanimously-elected-as-new-maharashtra-bjp-president-23582746</t>
+          <t>https://www.deccanherald.com/india/maharashtra/hindutva-not-against-any-religion-treating-all-religions-equally-is-true-secularism-nitin-gadkari-3611385</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.financialexpress.com/india-news/who-is-ravindra-chavan-four-time-mla-appointed-as-maharashtra-units-new-president/3899457/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/viral-list-of-dist-chiefs-fake-bjp-warns-of-police-action/articleshow/121252533.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/who-is-ravindra-chavan-new-maharashtra-bjp-chief-close-confidant-of-cm-devendra-fadnavis-2925029.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/justice-chavan-calls-for-national-judicial-service-reforms-to-address-vacancies-in-judiciary/articleshow/121299899.cms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/hindutva-not-against-any-religion-treating-all-religions-equally-is-true-secularism-nitin-gadkari-3611385</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-files-nomination-for-post-of-maharashtra-bjp-president-23582507</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-civic-polls-13214817.html</t>
+          <t>https://www.ptinews.com/story/national/ex-minister-ravindra-chavan-is-bjp's-new-maharashtra-unit-chief/2690729</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/viral-list-of-dist-chiefs-fake-bjp-warns-of-police-action/articleshow/121252533.cms</t>
+          <t>https://www.theweek.in/news/india/2025/07/01/who-is-ravindra-chavan-maharashtra-bjp-president-brings-congress-s-kunal-patil-into-party-fold.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/justice-chavan-calls-for-national-judicial-service-reforms-to-address-vacancies-in-judiciary/articleshow/121299899.cms</t>
+          <t>https://www.deccanherald.com/india/india-political-updates-latest-pm-narendra-modi-arvind-kejriwal-atishi-sanjay-singh-aap-bjp-congress-rahul-gandhi-delhi-assembly-elections-polls-live-politics-news-3350792</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-files-nomination-for-post-of-maharashtra-bjp-president-23582507</t>
+          <t>https://www.deccanherald.com/india/maharashtra/amit-shah-to-begin-3-day-maharashtra-visit-ahead-of-local-body-polls-3556463</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ex-minister-ravindra-chavan-is-bjp's-new-maharashtra-unit-chief/2690729</t>
+          <t>https://www.nagpurtoday.in/ravindra-chavan-appointed-maharashtra-bjp-president/07021333</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/money-lender-booked-for-suicide-abetment-of-debtor/articleshow/121603123.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/india-political-updates-latest-pm-narendra-modi-arvind-kejriwal-atishi-sanjay-singh-aap-bjp-congress-rahul-gandhi-delhi-assembly-elections-polls-live-politics-news-3350792</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/58-bjp-chiefs-of-districts-named/articleshow/121146293.cms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/amit-shah-to-begin-3-day-maharashtra-visit-ahead-of-local-body-polls-3556463</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-chief-in-maharashtra-brings-mns-union-workers-into-party/articleshow/123367896.cms</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/ravindra-chavan-appointed-maharashtra-bjp-president/07021333</t>
+          <t>https://www.aninews.in/news/national/politics/double-engine-govt-working-in-peoples-best-interests-new-maharashtra-bjp-chief-ravindra-chavan20250702021253</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/58-bjp-chiefs-of-districts-named/articleshow/121146293.cms</t>
+          <t>https://www.mid-day.com/news/india-news/article/indrayani-river-bridge-collapse-ex-minister-seeks-probe-into-delay-in-construction-of-new-structure-23571125</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/double-engine-govt-working-in-peoples-best-interests-new-maharashtra-bjp-chief-ravindra-chavan20250702021253</t>
+          <t>https://www.newsband.in/article_detail/dombivli-residents-demand-clarity-as-railways-issue-eviction-notices</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/indrayani-river-bridge-collapse-ex-minister-seeks-probe-into-delay-in-construction-of-new-structure-23571125</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bjps-sankalp-to-siddhi-campaign-to-begin-this-week/articleshow/121606429.cms</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://tennews.in/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
+          <t>https://tennews.in/ravindra-chavan-elected-unopposed-as-maha-bjp-chief/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/indigos-agile-employees-secure-record-salary-hike-in-historic-agreement-with-union/</t>
+          <t>https://tennews.in/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/bodies-of-pahalgam-terror-attack-victims-from-maharashtra-brought-to-mumbai-enn25042305870</t>
+          <t>https://thecsrjournal.in/indigos-agile-employees-secure-record-salary-hike-in-historic-agreement-with-union/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/ravindra-chavan-a-visionary-leader-strengthening-maharashtra-bjps-political-landscape.html</t>
+          <t>https://www.ptinews.com/editor-detail/Pune-Congress-leader-Sanjay-Jagtap-joins-BJP/2733730</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6725428</t>
+          <t>https://www.etvbharat.com/en/!state/bodies-of-pahalgam-terror-attack-victims-from-maharashtra-brought-to-mumbai-enn25042305870</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://gallinews.com/ravindra-chavan-bane-bjp-ke-naye-maharashtra-president/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/andheri-mla-ameet-satam-to-lead-mumbai-unit-as-party-gears-up-for-high-stakes-bmc-battle-23591113</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/bjp-picks-ravindra-chavan-as-maharashtra-chief-ahead-of-key-civic-polls.html</t>
+          <t>https://www.msn.com/en-in/news/India/ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra/ar-AA1JFbMn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/ravindra-chavan-appointed-as-bjp-state-president-of-maharashtra/</t>
+          <t>https://www.afternoonvoice.com/ravindra-chavan-a-visionary-leader-strengthening-maharashtra-bjps-political-landscape.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.cityairnews.com/content/ravindra-chavan-elected-unopposed-as-maha-bjp-chief</t>
+          <t>https://www.lokmattimes.com/national/bjps-idea-of-nationalism-will-be-taken-to-the-common-man-ravindra-chavan/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-appointed-ravindra-chavan-as-working-state-president-of-maharashtra-know-his-journey/articleshow/117154523.cms</t>
+          <t>https://news.abplive.com/news/india/ravindra-chavan-to-lead-maharashtra-bjp-telangana-andhra-uttarakhand-unit-chiefs-to-be-named-tomorrow-1784254</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/topic/ravindra-chavan</t>
+          <t>https://www.socialnews.xyz/?p=6725428</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-chief-of-maharashtra-bjp-ravindra-chavan-name-is-almost-finalised-9348436.html</t>
+          <t>https://gallinews.com/ravindra-chavan-bane-bjp-ke-naye-maharashtra-president/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/why-bjp-gave-responsibility-of-maharashtra-unit-to-ravindra-chavan-maratha-face-201736616683779.html</t>
+          <t>https://www.afternoonvoice.com/bjp-picks-ravindra-chavan-as-maharashtra-chief-ahead-of-key-civic-polls.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/ravindra-chavan-from-maharashtra-khandelwal-from-mp-became-new-state-president-of-bjp-know-all-details-here-8812249</t>
+          <t>https://www.sakshipost.com/news/ravindra-chavan-set-take-over-maharashtra-unit-bjp-chief-tomorrow-424218</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/bjp-may-appoint-ravindra-chavan-maharashtra-state-president-cm-devendra-fadnavis/3775586/</t>
+          <t>https://theindianawaaz.com/ravindra-chavan-appointed-as-bjp-state-president-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-why-party-appointed-know-all/articleshow/117210600.cms</t>
+          <t>https://trak.in/stories/2000-indigo-airlines-employees-officially-join-bjp-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/ravindra-chavan-new-maharashtra-bjp-president-know-his-political-journey-8811120</t>
+          <t>https://news.abplive.com/cities/ameet-satam-becomes-bjp-new-mumbai-chief-ahead-of-bmc-polls-who-is-he-1796474</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-ravindra-chavan-warns-throw-away-the-list-of-81-district-presidents-of-bjp-don-t-make-it-viral-social-media-1359706</t>
+          <t>https://www.cityairnews.com/content/ravindra-chavan-elected-unopposed-as-maha-bjp-chief</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/who-is-ravindra-chavan-bjp-mla-appointed-working-state-president-maharashtra-replace-chandrashekhar-bawankule-b507/</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-local-election-bjp-president-ravindra-chavan-asked-former-mps-and-mlas-to-adopt-one-mandal-each-ann-2988472</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/kalyan-ex-bjp-mla-feud-viral-clip-shows-strong-words-against-kapil-patil-and-ravindra-chavan-in-heated-exchange-9007785</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-appointed-ravindra-chavan-as-working-state-president-of-maharashtra-know-his-journey/articleshow/117154523.cms</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/maharashtra/ravindra-chauhan-on-the-post-of-bjp-maharashtra-state-president/</t>
+          <t>https://www.aajtak.in/topic/ravindra-chavan</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/bjp-news-ravindra-chavan-appointed-bjps-maharashtra-working-president-7451905</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-chief-of-maharashtra-bjp-ravindra-chavan-name-is-almost-finalised-9348436.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/bjp-state-president-ravindra-chavan-makes-big-statement-on-alliance-with-uddhav-thackeray-8864806</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-ravindra-chavan-can-become-president-of-maharashtra-bjp-mumbai-ann-2969682</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/ravindra-chavan-opens-up-about-disappointment-over-eknath-shinde-becoming-chief-minister-reveals-true-feelings-8865262</t>
+          <t>https://www.livehindustan.com/national/why-bjp-gave-responsibility-of-maharashtra-unit-to-ravindra-chavan-maratha-face-201736616683779.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-brahmin-obc-maratha-formula-ravindra-chouhan-chandrashekhar-bawankule-8954968.html</t>
+          <t>https://ndtv.in/india/ravindra-chavan-from-maharashtra-khandelwal-from-mp-became-new-state-president-of-bjp-know-all-details-here-8812249</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-elected-as-bjp-working-state-president-maharashtra-politics-marathi-news-1338059</t>
+          <t>https://www.jansatta.com/national/bjp-may-appoint-ravindra-chavan-maharashtra-state-president-cm-devendra-fadnavis/3775586/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/bjp-state-working-president-ravindra-chavan-responds-congress-state-president-harshvardhan-sapkal-8802075</t>
+          <t>https://politalks.news/ravindra-chavan-biography-in-hindi</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ravindra-chavan-appointed-maharashtra-bjp-president-1436968.html</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/ravindra-chavan-becomes-maharashtra-bjp-new-president-know-political-career-ntc-rpti-2277379-2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-politics-bjp-leader-ravindra-chavan-unanimously-elected-maharashtra-bjp-president-80826</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-why-party-appointed-know-all/articleshow/117210600.cms</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/mla-ravindra-chavan-has-been-appointed-as-the-maharashtra-state-executive-president-of-bjp/</t>
+          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-name-suggested-as-maharashtra-bjp-president-by-chandrashekhar-bawankule-2971280</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/congress-mp-ravindra-chavan-warning-to-follow-protocol-due-to-nanded-municipal-corporation-commissioner-over-not-inviting-for-programme-1360903</t>
+          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-appointed-maharashtra-bjp-working-president-cm-devendra-fadnavis-welcomes-2861067</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-appointed-as-bjp-state-working-president-by-j-p-nadda/articleshow/117154533.cms</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/ravindra-chavan-became-the-new-president-of-maharashtra-bjp-took-this-promise-1329755.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/ravindra-chavan-to-be-new-maharashtra-bjp-president-show-of-power-at-aaditya-thackeray-constituency-1425668.html</t>
+          <t>https://ndtv.in/maharashtra-news/ravindra-chavan-new-maharashtra-bjp-president-know-his-political-journey-8811120</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/bjp-ravindra-chavan-news-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%9F-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-maharashtra-politics/vi-AA1K12wX</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-ravindra-chavan-warns-throw-away-the-list-of-81-district-presidents-of-bjp-don-t-make-it-viral-social-media-1359706</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/30/from-party-worker-to-state-president.html</t>
+          <t>https://www.lokmatnews.in/india/who-is-ravindra-chavan-bjp-mla-appointed-working-state-president-maharashtra-replace-chandrashekhar-bawankule-b507/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/mahayuti-news-unveiling-of-chhatrapati-shivaji-maharaj-statue-in-dombivli-shiv-sena-shinde-faction-criticizes-bjp-mla-ravindra-chavan-7945018</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/bjp-maharashtra-president-ravindra-chavan-kunal-patil-congress-north-maharashtra-dhule-ntcpbt-dskc-2277786-2025-07-02</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/3/the-theme-of-the-dombivalikar-friendship-run-was-unveiled-by-bjp-state-president-ravindra-chavan.html</t>
+          <t>https://marathi.ndtv.com/cities/kalyan-ex-bjp-mla-feud-viral-clip-shows-strong-words-against-kapil-patil-and-ravindra-chavan-in-heated-exchange-9007785</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bjp-leadership-meet-ravindra-chavan-meets-jp-nadda-in-delhi-first-meeting-as-state-president-earlier-met-amit-shah-in-pune-1368594</t>
+          <t>https://mandalnews.com/maharashtra/ravindra-chauhan-on-the-post-of-bjp-maharashtra-state-president/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-bjp-news-ravindra-chavan-appointed-as-bjp-state-president/</t>
+          <t>https://marathi.ndtv.com/cities/bjp-news-ravindra-chavan-appointed-bjps-maharashtra-working-president-7451905</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-bjp-news-former-minister-ravindra-chavan-files-application-for-bjp-state-president-post/</t>
+          <t>https://marathi.ndtv.com/politics/bjp-state-president-ravindra-chavan-makes-big-statement-on-alliance-with-uddhav-thackeray-8864806</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/tv-show/majha-vishesh/maharashtra-bjp-president-ravindra-chavan-s-first-interview-reveals-role-in-operation-shinde-discusses-mahayuti-election-strategy-it-notices-and-marathi-politics-1369435</t>
+          <t>https://marathi.ndtv.com/politics/ravindra-chavan-opens-up-about-disappointment-over-eknath-shinde-becoming-chief-minister-reveals-true-feelings-8865262</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-and-local-body-polls/articleshow/122185894.cms</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-elected-as-bjp-working-state-president-maharashtra-politics-marathi-news-1338059</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/ravindra-chavan-says-thanks-to-his-party-after-selected-for-bjp-maharashtra-president/articleshow/122185577.cms</t>
+          <t>https://marathi.ndtv.com/politics/bjp-state-working-president-ravindra-chavan-responds-congress-state-president-harshvardhan-sapkal-8802075</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/31/adopt-one-mandal-each-and-resolve-to-build-an-organization-state-president-ravindra-chavan-appeals-to-former-m.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-brahmin-obc-maratha-formula-ravindra-chouhan-chandrashekhar-bawankule-8954968.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-may-be-elected-as-bjp-state-president-for-maharashtra-marathi-news/articleshow/122124651.cms</t>
+          <t>https://www.tv9marathi.com/videos/ravindra-chavan-appointed-maharashtra-bjp-president-1436968.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/bjp-state-president-ravindra-chavan-good-luck-minister-vikhe-patil-rahata/</t>
+          <t>https://www.abplive.com/states/maharashtra/annasaheb-dange-joins-bjp-with-his-two-sons-chiman-and-vishwanath-dange-in-the-presence-of-cm-devendra-fadnavis-ann-2987987</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-amit-satam-elected-as-mumbai-president-of-bjp-cm-devendra-fadnavis-9153593</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-politics-bjp-leader-ravindra-chavan-unanimously-elected-maharashtra-bjp-president-80826</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-bjp-calls-urgent-meeting-in-mumbai-raj-thackeray-takes-aggressive-stance-on-matak-sodi-allegations-1379525</t>
+          <t>https://marathi.abplive.com/news/nanded/congress-mp-ravindra-chavan-warning-to-follow-protocol-due-to-nanded-municipal-corporation-commissioner-over-not-inviting-for-programme-1360903</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/photogallery/news/ravindra-chavan-important-role-when-eknath-shinde-takeover-shiv-sena/photoshow/122188079.cms</t>
+          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-appointed-as-bjp-state-working-president-by-j-p-nadda/articleshow/117154533.cms</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/bjp-live-devendra-fadnavis-annasaheb-dange-join-bjp-30th-july-ravindra-chavan-chardrakant-patil/907022/</t>
+          <t>https://navbharattimes.indiatimes.com/india/bjp-announces-new-state-presidents-in-4-states-changes-in-maharashtra-uttarakhand-telangana-and-himachal-pradesh/articleshow/122163940.cms</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/big-changes-underway-in-bjp-kdmc-ahead-of-municipal-elections/articleshow/121160143.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/bjp-will-get-a-new-maharashtra-president-ravindra-chavan-will-be-appointed-in-place-of-chandrashekhar-bawankule-1366663</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-politics-1500-members-of-uddhav-thackerays-party-join-bjp-party-entry-in-mumbai-in-the-presence-of-ravindra-chavan/910127</t>
+          <t>https://news18marathi.com/maharashtra/ravindra-chavan-to-be-new-maharashtra-bjp-president-show-of-power-at-aaditya-thackeray-constituency-1425668.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/dahi-handi-2025-dahi-handi-celebrated-in-a-traditional-manner-in-dombivli-bjp-mla-ravindra-chavan/912575/</t>
+          <t>https://www.msn.com/mr-in/news/other/bjp-ravindra-chavan-news-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%9F-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-maharashtra-politics/vi-AA1K12wX</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sudhakar-badgujar-bjp-chandrashekhar-bawankule-he-join-bjp-with-girish-mahajan-and-ravindra-chavan-1364736</t>
+          <t>https://marathi.abplive.com/news/maharashtra/ravindra-chavan-bjp-new-president-profile-dombivli-mla-maharashtra-mumbai-politics-marathi-news-1367337</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nanded/set-back-for-bjp-ashok-chavan-discussion-on-alliance-between-congress-and-prakash-ambedkar-vanchit-bahujan-aghadi/articleshow/122873066.cms</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-134276483.html</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/nanded-news-congress-and-vanchit-hint-at-alliance-for-local-government-elections-in-nanded-will-consider-proposal-if-received-1371522</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/30/from-party-worker-to-state-president.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/bjp-leader-vikas-mhatre-resigns-from-bjp-ahead-dombivli-mahapalika-election-allegation-on-ravindra-chavan-1423215.html</t>
+          <t>https://www.aajtak.in/programmes/mumbai-metro/video/bjp-appointed-ravindra-chavan-as-maharashtra-unit-cheif-mumbai-metro-frvd-2277550-2025-07-02</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/dhule-congress-leader-kunal-patil-dismisses-rumors-of-joining-bjp-maharashtra-news-mhs25062501797</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/3/the-theme-of-the-dombivalikar-friendship-run-was-unveiled-by-bjp-state-president-ravindra-chavan.html</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/youth-leader-vishal-parab-joins-bjp/</t>
+          <t>https://news18marathi.com/maharashtra/ravindra-chavan-aggressive-on-home-ground-kdmc-election-eknath-shinde-led-shiv-sena-faced-trouble-1450204.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/shetkari-kamgar-paksha-skp-jayant-patils-brother-pandit-patil-to-join-bjp-mumbai-maharashtra-maharashtra-news-mhs25041603477</t>
+          <t>https://www.patrika.com/mumbai-news/youtuber-shirish-gavas-passed-away-red-soil-stories-channel-33-year-old-founder-died-19834284</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-misssion-mumbai-bjp-will-turn-the-tables-meeting-for-the-post-of-mumbai-president-on-place-of-ashish-shelar-two-mlas-put-forward-their-names-pravin-darekar-1354321</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bjp-leadership-meet-ravindra-chavan-meets-jp-nadda-in-delhi-first-meeting-as-state-president-earlier-met-amit-shah-in-pune-1368594</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/raigad/shivsena-mla-mahendra-thorve-join-bjp-in-raigad-before-local-government-elections-marathi-news/articleshow/121927356.cms</t>
+          <t>https://deshdoot.com/maharashtra-bjp-news-former-minister-ravindra-chavan-files-application-for-bjp-state-president-post/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/former-congress-mla-kailash-gorantyal-joins-bjp-major-challenge-for-shinde-led-shiv-sena-in-jalna/articleshow/123019959.cms</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-former-congress-mla-kunal-patil-likely-to-join-bjp-meets-ravindra-chavan-in-mumbai-marathi-news-1365750</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/photogallery/news/congress-leader-kunal-patil-may-be-join-bjp-soon/photoshow/122030946.cms</t>
+          <t>https://www.localnewsnetwork.in/bjp-needs-a-mayor-to-remove-the-development-eclipse-of-kalyan-dombivali-bjp-state-president-ravindra-chavan/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/--20250502182005/</t>
+          <t>https://marathi.abplive.com/tv-show/majha-vishesh/maharashtra-bjp-president-ravindra-chavan-s-first-interview-reveals-role-in-operation-shinde-discusses-mahayuti-election-strategy-it-notices-and-marathi-politics-1369435</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/bjp-will-soon-get-a-new-state-president-ravindra-chavan-will-be-entrusted-with-the-responsibility/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-and-local-body-polls/articleshow/122185894.cms</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/bjp-will-get-a-new-state-president-today-ravindra-chavan-will-accept-the-oath/</t>
+          <t>https://www.tv9marathi.com/maharashtra/bjp-state-president-ravindra-chavan-big-statement-regarding-municipal-elections-shiv-sena-tension-will-increase-1460977.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/four-former-corporators-of-ubatha-in-malvan-join-bjp-along-with-their-supporters/cid1752483678.htm</t>
+          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/ravindra-chavan-says-thanks-to-his-party-after-selected-for-bjp-maharashtra-president/articleshow/122185577.cms</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/bhor-mulshi-taluka-workers-from-various-parties-join-bjp/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/31/adopt-one-mandal-each-and-resolve-to-build-an-organization-state-president-ravindra-chavan-appeals-to-former-m.html</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/activist-of-ubt-sharad-pawar-group-and-congress-in-shahapur-taluka-join-bjp/</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-exclusive-interview-talk-about-will-there-be-challenge-to-bjp-if-raj-thackeray-uddhav-thackeray-come-together-maharashtra-politics-marathi-news-1369421</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-former-corporators-from-kalyan-dombivli-chandrapur-districts-join-bjp/</t>
+          <t>https://marathi.abplive.com/news/politics/congress-leader-kailash-gorantyal-and-suresh-varpudkar-will-join-bjp-under-the-leadership-of-state-president-ravindra-chavan-at-mumbai-jalna-constituency-before-election-1373052</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/big-news-ravindra-chavan-elected-as-bjps-working-regional-president/108447/</t>
+          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-may-be-elected-as-bjp-state-president-for-maharashtra-marathi-news/articleshow/122124651.cms</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/bjp-president-banner-tore-the-of-state-election/</t>
+          <t>https://deshdoot.com/bjp-state-president-ravindra-chavan-good-luck-minister-vikhe-patil-rahata/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/07/ravindra-shinde-joins-bjp/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/nitesh-rane-and-gopichand-padalkar-bjp-gave-direct-warning-ravindra-chavan-on-bjp-leaders-maharashtra-politics/925249</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-ravindra-chavan-talks-on-uddhav-thackeray-raj-thackeray-reunite-bmc-elections-2025/articleshow/123154745.cms</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-amit-satam-elected-as-mumbai-president-of-bjp-cm-devendra-fadnavis-9153593</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/mumbai/ravindra-chavan-has-become-the-new-bjp-maharashtra-president-1426306.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-bjp-calls-urgent-meeting-in-mumbai-raj-thackeray-takes-aggressive-stance-on-matak-sodi-allegations-1379525</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/photo-gallery/ravindra-chavan-appealed-to-the-workers-after-assuming-the-post-of-bjp-state-president/898007/</t>
+          <t>https://www.tv9marathi.com/videos/sanjay-raut-slams-ravindra-chavan-over-indrayani-river-bridge-collapse-accident-1424794.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-bjp-maharashtra-state-president-election-nomination-process-begins-ravindra-chavhan-likely-to-secure-position-1367011</t>
+          <t>https://marathi.indiatimes.com/photogallery/news/ravindra-chavan-important-role-when-eknath-shinde-takeover-shiv-sena/photoshow/122188079.cms</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/four-former-corporators-of-ubt-in-malvan-join-bjp-along-with-their-supporters-welcomed-by-bjp-state-president-ravindra-chavan-maharashtra-news-mhs25071403115</t>
+          <t>https://www.mymahanagar.com/mahamumbai/bjp-live-devendra-fadnavis-annasaheb-dange-join-bjp-30th-july-ravindra-chavan-chardrakant-patil/907022/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/former-nagsevaks-and-activists-of-bva-of-vasai-virar-join-bjp/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/big-changes-underway-in-bjp-kdmc-ahead-of-municipal-elections/articleshow/121160143.cms</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%AD%E0%A4%BE%E0%A4%9C%E0%A4%AA%E0%A4%BE-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%BE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B0%E0%A4%B5%E0%A5%80%E0%A4%82/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/dahi-handi-2025-dahi-handi-celebrated-in-a-traditional-manner-in-dombivli-bjp-mla-ravindra-chavan/912575/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-gb/news/world/kedar-jadhav-makes-bold-prediction-about-india-playing-pakistan-in-asia-cup/ar-AA1KJnU4</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nanded/set-back-for-bjp-ashok-chavan-discussion-on-alliance-between-congress-and-prakash-ambedkar-vanchit-bahujan-aghadi/articleshow/122873066.cms</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/4-ex-congress-corporators-join-bjp-in-kalyan-dombivli/articleshow/123447826.cms</t>
+          <t>https://marathi.abplive.com/news/politics/sudhakar-badgujar-bjp-chandrashekhar-bawankule-he-join-bjp-with-girish-mahajan-and-ravindra-chavan-1364736</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
+          <t>https://marathi.abplive.com/news/nanded/nanded-news-congress-and-vanchit-hint-at-alliance-for-local-government-elections-in-nanded-will-consider-proposal-if-received-1371522</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-inducts-key-pwp-leaders-before-local-body-elections-101744831159344.html</t>
+          <t>https://news18marathi.com/maharashtra/bjp-leader-vikas-mhatre-resigns-from-bjp-ahead-dombivli-mahapalika-election-allegation-on-ravindra-chavan-1423215.html</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/politics/news/no-one-becomes-great-by-imposing-themselves-nitin-gadkari-warns-against-arrogance-in-leadership-cong-reacts-11752387796290.html</t>
+          <t>https://www.tarunbharat.com/youth-leader-vishal-parab-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-misssion-mumbai-bjp-will-turn-the-tables-meeting-for-the-post-of-mumbai-president-on-place-of-ashish-shelar-two-mlas-put-forward-their-names-pravin-darekar-1354321</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cabinet-reshuffle-on-cards-fadnavis-meets-shah-nadda-in-delhi-3648744</t>
+          <t>https://marathi.indiatimes.com/maharashtra/raigad/shivsena-mla-mahendra-thorve-join-bjp-in-raigad-before-local-government-elections-marathi-news/articleshow/121927356.cms</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Pune-Congress-leader-Sanjay-Jagtap-joins-BJP/2733730</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/former-congress-mla-kailash-gorantyal-joins-bjp-major-challenge-for-shinde-led-shiv-sena-in-jalna/articleshow/123019959.cms</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/ncp-shiv-sena-ubt-members-join-bjp-in-nashik/articleshow/122233115.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chief-minister-devendra-fadnavis-reaction-regarding-marathi-language-criticism-on-uddhav-thackeray-in-mumbai-1367354</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/congress-ex-mla-suresh-warpudkar-and-family-set-to-join-bjp/articleshow/122951927.cms</t>
+          <t>https://marathi.indiatimes.com/photogallery/news/congress-leader-kunal-patil-may-be-join-bjp-soon/photoshow/122030946.cms</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/bjp-state-chiefs-kharges-high-command-remark-congress-bihar-elections-modi-sonia-rahul-gandhi-socialist-secular-rss-constitution-india-tamil-nadu-3610086</t>
+          <t>https://www.khabar24.tv/2025/07/02/after-the-brilliant-tenure-of-chandrashekhar-bawankule-the-command-of-maharashtra-bjp-is-now-in-the-hands-of-ravindra-chavan/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/emotional-farewell-outgoing-bjp-state-president-bawankule-pens-heartfelt-letter-to-party-workers/07021355</t>
+          <t>https://www.newsnationtv.com/--20250502182005/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/bjp-state-presidents-appointment-national-president-election-july-maharashtra-himachal-pm-modi-jp-nadda-135348404.html</t>
+          <t>https://www.dainikprabhat.com/bjp-will-soon-get-a-new-state-president-ravindra-chavan-will-be-entrusted-with-the-responsibility/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://english.publictv.in/bjp-announces-new-state-chiefs-in-7-states-2-uts-moves-closer-to-elect-national-president/</t>
+          <t>https://www.marathiebatmya.com/political/former-nagsevaks-and-activists-of-bva-of-vasai-virar-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-mp-murlidhar-mohol-launches-citys-first-24x7-digital-citizen-service-office/</t>
+          <t>https://www.marathiebatmya.com/political/bhor-mulshi-taluka-workers-from-various-parties-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://kknlive.com/en/andhra-pradesh-en/bjp-appoints-new-state-presidents-in-9-states/</t>
+          <t>https://www.marathiebatmya.com/political/activist-of-ubt-sharad-pawar-group-and-congress-in-shahapur-taluka-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://fox5sandiego.com/business/press-releases/ein-presswire/827256708/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy</t>
+          <t>https://www.marathiebatmya.com/political/many-former-corporators-from-kalyan-dombivli-chandrapur-districts-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/ex-minister-ravindra-chavan-files-nomination-for-maharashtra-bjp-chief-post-8800476</t>
+          <t>https://www.timemaharashtra.com/maharashtra/big-news-ravindra-chavan-elected-as-bjps-working-regional-president/108447/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bjp-leader-ravindra-chavan-appointed-as-new-state-president-of-maharashtra/</t>
+          <t>https://deshonnati.com/bjp-president-banner-tore-the-of-state-election/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://tennews.in/ravindra-chavan-elected-unopposed-as-maha-bjp-chief/</t>
+          <t>https://news34.in/2025/07/ravindra-shinde-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/andheri-mla-ameet-satam-to-lead-mumbai-unit-as-party-gears-up-for-high-stakes-bmc-battle-23591113</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-ravindra-chavan-talks-on-uddhav-thackeray-raj-thackeray-reunite-bmc-elections-2025/articleshow/123154745.cms</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/who-is-ravindra-chavan-new-bjp-president-for-maharashtra-close-aide-of-cm-fadnavis-8810167</t>
+          <t>https://www.mymahanagar.com/photo-gallery/ravindra-chavan-appealed-to-the-workers-after-assuming-the-post-of-bjp-state-president/898007/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-to-appoints-ravindra-chavan-next-bjp-president-of-maharashtra-chandrashekhar-bawankule-amit-shah-visit-know-all/articleshow/121479121.cms</t>
+          <t>https://marathi.abplive.com/videos/news/politics-bjp-maharashtra-state-president-election-nomination-process-begins-ravindra-chavhan-likely-to-secure-position-1367011</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/maharashtra-ravindra-chavan-set-to-become-new-president-of-state-bjp-said-sources-2025-06-30-1146038</t>
+          <t>https://pcbtoday.in/%E0%A4%AD%E0%A4%BE%E0%A4%9C%E0%A4%AA%E0%A4%BE-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%BE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B0%E0%A4%B5%E0%A5%80%E0%A4%82/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/hindi/trends/maharashtra-bjp-gets-new-state-chief-heres-all-about-newly-appointed-party-president-ravindra-chavan-know-who-is-he-241751382375965.html</t>
+          <t>https://www.msn.com/en-gb/news/world/kedar-jadhav-makes-bold-prediction-about-india-playing-pakistan-in-asia-cup/ar-AA1KJnU4</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-visited-sai-baba-in-shirdi-after-being-appointed-as-state-executive-president-of-bjp-maharashtra-marathi-news-1338130</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/4-ex-congress-corporators-join-bjp-in-kalyan-dombivli/articleshow/123447826.cms</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/hemant-khandelwal-will-be-the-new-president-of-madhya-pradesh-bjp-8808221</t>
+          <t>https://zeenews.india.com/india/who-is-ravindra-chavan-new-maharashtra-bjp-chief-close-confidant-of-cm-devendra-fadnavis-2925029.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/ravindra-chavan-elected-unopposed-as-new-state-president-of-bharatiya-janata-party/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-inducts-key-pwp-leaders-before-local-body-elections-101744831159344.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-bjp-likely-to-contest-alone-amid-mumbai-bmc-polls-with-eknath-shinde-and-ajit-pawar-amit-shah-ravindra-chavan-meet/articleshow/122897869.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-new-strength-in-bjp-organizational-building-appointments-of-963-mandal-presidents-completed-by-ravindra-chavan-marathi-news-1355302</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ahead-of-local-body-polls-bjp-finalises-names-of-22-district-presidents/articleshow/121549544.cms</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-maharashtra-annouces-50-district-president-navi-mumbai-rajesh-patil-mira-bhayandar-dilip-jain-check-full-list/articleshow/121136990.cms</t>
+          <t>https://www.livemint.com/politics/news/no-one-becomes-great-by-imposing-themselves-nitin-gadkari-warns-against-arrogance-in-leadership-cong-reacts-11752387796290.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-maharashtra-bjp-president-likely-to-contest-mumbai-cricket-association-mca-election-in-november-after-delhi-visit-1374335</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cabinet-reshuffle-on-cards-fadnavis-meets-shah-nadda-in-delhi-3648744</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/bjp-maharashtra-ravindra-chavan-set-to-be-elected-as-state-president-unopposed-formal-announcement-expected-tomorrow-1367175</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/ncp-shiv-sena-ubt-members-join-bjp-in-nashik/articleshow/122233115.cms</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-bjp-party-maharashtra-state-president-after-sthanik-swarajya-sanstha-election-chandrashekhar-bawankule-maharashtra-news-12-jan-2025-abp-majha-1338092</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/congress-ex-mla-suresh-warpudkar-and-family-set-to-join-bjp/articleshow/122951927.cms</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/editorial/will-ravindra-chavan-meet-the-challenge-of-the-bjp-state-president-in-marathi/898320/</t>
+          <t>https://www.deccanherald.com/india/bjp-state-chiefs-kharges-high-command-remark-congress-bihar-elections-modi-sonia-rahul-gandhi-socialist-secular-rss-constitution-india-tamil-nadu-3610086</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ravindra-chavan-elected-bjp-maharashtra-president-1436164.html</t>
+          <t>https://www.aninews.in/news/national/general-news/public-gave-us-landslide-victory-dy-cm-eknath-shinde-exerts-confidence-on-win-of-mahayuti-in-maharashtra-elections20250702090322</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-state-president-ravindra-chavan-held-meeting-former-mps-mlas-for-preparation-upcoming-local-body-elections/articleshow/123032835.cms</t>
+          <t>https://www.nagpurtoday.in/emotional-farewell-outgoing-bjp-state-president-bawankule-pens-heartfelt-letter-to-party-workers/07021355</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/ravindra-chavan-state-president-of-maharashtra-bjp-who-says-bjp-is-my-identity-276739/amp/</t>
+          <t>https://www.bhaskarenglish.in/national/news/bjp-state-presidents-appointment-national-president-election-july-maharashtra-himachal-pm-modi-jp-nadda-135348404.html</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/who-is-ravindra-chavan-ravindra-chavan-becomes-the-working-president-of-maharashtra-bjp-national-president-jp-nadda-announced-50716</t>
+          <t>https://english.publictv.in/bjp-announces-new-state-chiefs-in-7-states-2-uts-moves-closer-to-elect-national-president/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/ravindra-chavan-appointed-as-bjp-state-president/</t>
+          <t>https://kknlive.com/en/andhra-pradesh-en/bjp-appoints-new-state-presidents-in-9-states/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-party-joining-key-congress-and-thackeray-shiv-sena-office-bearers-join-bjp-in-maharashtra-under-ravindra-chavan-s-leadership-1374978</t>
+          <t>https://fox5sandiego.com/business/press-releases/ein-presswire/827256708/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
+          <t>https://www.ndtv.com/india-news/ex-minister-ravindra-chavan-files-nomination-for-maharashtra-bjp-chief-post-8800476</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavhan-to-become-12th-bjp-maharashtra-state-president-succeeding-a-long-line-of-leaders-in-party-s-45-year-history-1366862</t>
+          <t>https://www.tribuneindia.com/news/business/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-bjp-to-announce-ravindra-chavan-as-maharashtra-state-president-on-july-1-massive-party-gathering-planned-1366858</t>
+          <t>https://ndtv.in/india/who-is-ravindra-chavan-new-bjp-president-for-maharashtra-close-aide-of-cm-fadnavis-8810167</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/ravindra-chavan-unanimously-elected-maharashtra-bjp-president-faces-local-body-election-challenges-1367369</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-to-appoints-ravindra-chavan-next-bjp-president-of-maharashtra-chandrashekhar-bawankule-amit-shah-visit-know-all/articleshow/121479121.cms</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-ravindra-chavan-on-thackeray-brothers-alliance-mahayuti-bmc-election-strategy-hindi-marathi-controversy-1444066.html</t>
+          <t>https://ndtv.in/india/hemant-khandelwal-will-be-the-new-president-of-madhya-pradesh-bjp-8808221</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/web-stories/politics/who-is-bharatiya-janata-party-state-president-of-maharashtra-ravindra-chavan-bjp-1367338</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-bjp-likely-to-contest-alone-amid-mumbai-bmc-polls-with-eknath-shinde-and-ajit-pawar-amit-shah-ravindra-chavan-meet/articleshow/122897869.cms</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-big-announcement-from-bjp-amit-satam-elected-as-mumbai-city-president/articleshow/123494762.cms</t>
+          <t>https://marathi.hindustantimes.com/maharashtra/ravindra-chavan-elected-as-bjp-working-state-president-why-bjp-gave-responsibility-141736618335892.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/who-is-ravindra-chavan-devendra-fadnavis-confidant-ravindra-chavan-elected-as-bjps-new-state-president-article-152194052</t>
+          <t>https://marathi.abplive.com/news/maharashtra/kedar-jadhav-to-join-bjp-in-presence-maharashtra-cm-devendra-fadnavis-ravindra-chavan-mumbai-marathi-news-1353247</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-corona-update-rain-update-monsoon-ajchya-thalak-batmya-on-july-01-political-news-in-marathi-919652</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-new-strength-in-bjp-organizational-building-appointments-of-963-mandal-presidents-completed-by-ravindra-chavan-marathi-news-1355302</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/ravindra-chavan-named-maharashtra-bjp-president-fadnavis-loyalist-savarkar-follower-who-is-ravindra-chavan-profile-1784513</t>
+          <t>https://marathi.abplive.com/news/pune/pune-news-sanjay-jagtap-joins-bjp-ravindra-chavan-s-presence-big-blow-to-congress-before-upcoming-elections-1370379</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/mumbai-receives-bodies-of-pahalgam-terror-attack-victims-134898349.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-maharashtra-bjp-president-likely-to-contest-mumbai-cricket-association-mca-election-in-november-after-delhi-visit-1374335</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-convention-starts-in-shirdi-speculation-fumes-for-new-state-president-know-all/articleshow/117149931.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-maharashtra-annouces-50-district-president-navi-mumbai-rajesh-patil-mira-bhayandar-dilip-jain-check-full-list/articleshow/121136990.cms</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/ravindra-jadeja-relation-with-bihar-journey-from-mahendra-singh-chauhan-to-dhoni/articleshow/121551590.cms</t>
+          <t>https://marathi.abplive.com/videos/news/bjp-maharashtra-ravindra-chavan-set-to-be-elected-as-state-president-unopposed-formal-announcement-expected-tomorrow-1367175</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/crew-member-roshni-songhare-died-in-air-india-plane-crash-in-ahmedabad-2025-06-12-1142268</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-bjp-party-maharashtra-state-president-after-sthanik-swarajya-sanstha-election-chandrashekhar-bawankule-maharashtra-news-12-jan-2025-abp-majha-1338092</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.nayaindia.com/news/bjp-presidents-of-three-states-decided/499890.html</t>
+          <t>https://www.mymahanagar.com/editorial/will-ravindra-chavan-meet-the-challenge-of-the-bjp-state-president-in-marathi/898320/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://globalgreenews.com/2025/07/02/maharashtra-bjp-leader-ravindra-chavan-appointed-as-new-state-president/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-state-president-ravindra-chavan-held-meeting-former-mps-mlas-for-preparation-upcoming-local-body-elections/articleshow/123032835.cms</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/former-cricketer-kedar-jadhav-joins-bjp-8118085</t>
+          <t>https://thefocusindia.com/maharashtra-news/ravindra-chavan-state-president-of-maharashtra-bjp-who-says-bjp-is-my-identity-276739/amp/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-chief-in-maharashtra-brings-mns-union-workers-into-party/articleshow/123367896.cms</t>
+          <t>https://marathi.abplive.com/news/politics/operation-eknath-shinde-had-a-big-responsibility-he-said-that-fadnavis-would-not-become-the-chief-minister-so-he-had-tears-in-his-eyes-story-told-by-ravindra-chavan-1369426</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/ahead-of-civic-polls-maharashtra-bjp-chief-stakes-claim-for-kdmc-mayors-post/articleshow/123077307.cms</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/who-is-ravindra-chavan-ravindra-chavan-becomes-the-working-president-of-maharashtra-bjp-national-president-jp-nadda-announced-50716</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ahead-of-local-body-polls-bjp-finalises-names-of-22-district-presidents/articleshow/121549544.cms</t>
+          <t>https://www.tarunbharat.com/ravindra-chavan-appointed-as-bjp-state-president/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra-23587437</t>
+          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra/ar-AA1JFbMn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-party-joining-key-congress-and-thackeray-shiv-sena-office-bearers-join-bjp-in-maharashtra-under-ravindra-chavan-s-leadership-1374978</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278530942/bjp-mla-amit-satam-announced-as-president-of-mumbai-unit-ahead-of-bmc-polls</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavhan-to-become-12th-bjp-maharashtra-state-president-succeeding-a-long-line-of-leaders-in-party-s-45-year-history-1366862</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
+          <t>https://marathi.abplive.com/videos/news/politics-bjp-to-announce-ravindra-chavan-as-maharashtra-state-president-on-july-1-massive-party-gathering-planned-1366858</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/3/KDMC-Dr-Nanasaheb-Dharmadhikari-Pratishthan-Cleanliness-Campaign.html</t>
+          <t>https://marathi.abplive.com/videos/news/ravindra-chavan-unanimously-elected-maharashtra-bjp-president-faces-local-body-election-challenges-1367369</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
+          <t>https://marathi.abplive.com/web-stories/politics/who-is-bharatiya-janata-party-state-president-of-maharashtra-ravindra-chavan-bjp-1367338</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/pune-bridge-collapse-new-bridge-sanctioned-a-year-ago-but-work-order-came-on-june-10-101750128084734.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/who-is-ravindra-chavan-devendra-fadnavis-confidant-ravindra-chavan-elected-as-bjps-new-state-president-article-152194052</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/centre-removes-turkish-firm-celebi-from-ground-handling-at-mumbai-airport/articleshow/122106708.cms</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-visited-sai-baba-in-shirdi-after-being-appointed-as-state-executive-president-of-bjp-maharashtra-marathi-news-1338130</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/rajendra-gavit-bjp-mla-second-marriage-hc-10086135/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-corona-update-rain-update-monsoon-ajchya-thalak-batmya-on-july-01-political-news-in-marathi-919652</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/27/eknath-shinde-on-iconic-building-in-Mumbai.html</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-june-maharashtra-assembly-monsoon-session-2025-of-the-legislature-begins-today-mahayuti-government-devendra-fadanvis-ajit-pawar-eknath-shinde-gkt-96-5192359/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-trilingual-policy-narendra-jadhav-committee-raj-thackeray-opposition-language-review-rm82</t>
+          <t>https://news.abplive.com/cities/ravindra-chavan-named-maharashtra-bjp-president-fadnavis-loyalist-savarkar-follower-who-is-ravindra-chavan-profile-1784513</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/ravindra-chavan-elected-as-bjp-state-president/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-convention-starts-in-shirdi-speculation-fumes-for-new-state-president-know-all/articleshow/117149931.cms</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/ravindra-jadeja-relation-with-bihar-journey-from-mahendra-singh-chauhan-to-dhoni/articleshow/121551590.cms</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-assembly-monsoon-session-2025-live-updates-mahayuti-vs-mva-cm-devendra-fadnavis-8804189</t>
+          <t>https://www.nayaindia.com/news/bjp-presidents-of-three-states-decided/499890.html</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/mumbai-bjp-mla-amit-satam-becomes-mumbai-bjp-president/</t>
+          <t>https://www.aajtak.in/india/maharashtra/video/maharashtra-bjp-has-a-new-president-ravindra-chavan-has-become-the-state-head-ytvd-2277534-2025-07-02</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
+        <is>
+          <t>https://globalgreenews.com/2025/07/02/maharashtra-bjp-leader-ravindra-chavan-appointed-as-new-state-president/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/thane/ahead-of-civic-polls-maharashtra-bjp-chief-stakes-claim-for-kdmc-mayors-post/articleshow/123077307.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>https://www.ndtv.com/india-news/former-cricketer-kedar-jadhav-joins-bjp-8118085</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/3/27/eknath-shinde-on-iconic-building-in-Mumbai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-trilingual-policy-narendra-jadhav-committee-raj-thackeray-opposition-language-review-rm82</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/bjp-new-list-of-58-district-presidents-announced-in-the-state-with-mumbai-preparations-for-elections-devendra-fadnavis-chandrashekhar-bawankule-marathi-news-1358929</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>https://www.marathi.hindusthanpost.com/politics/ravindra-chavan-elected-as-bjp-state-president/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-assembly-monsoon-session-2025-live-updates-mahayuti-vs-mva-cm-devendra-fadnavis-8804189</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
         <is>
           <t>https://www.deccanherald.com/india/maharashtra/bjp-holds-meeting-of-former-mps-and-mlas-ahead-of-local-body-polls-in-maharashtra-3658754</t>
         </is>

--- a/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,182 +438,252 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nda-candidates-win-in-vp-poll-testament-to-modis-leadership-chavan/articleshow/123816248.cms</t>
+          <t>http://www.msn.com/en-in/news/India/dombivli-mla-ravindra-chavan-to-be-appointed-maharashtra-bjp-prez/ar-AA1HJbtF?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-illegal-building-demolition-halted-in-dombivli-as-urban-development-department-summons-kdmc-chief/articleshow/123789657.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%AB-%E0%A4%B8%E0%A5%87-%E0%A4%9F-%E0%A4%95%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A4%A3-%E0%A4%A4-%E0%A4%B2-%E0%A4%AE%E0%A4%A4%E0%A4%A6-%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B5%E0%A4%B3%E0%A4%B2%E0%A5%87-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B0-%E0%A4%A3%E0%A5%87-%E0%A4%95%E0%A5%81%E0%A4%9F%E0%A5%81%E0%A4%82%E0%A4%AC-%E0%A4%B8-%E0%A4%A0-%E0%A4%A7-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%98%E0%A4%82%E0%A4%9F/ar-AA1v1SPv?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/09/mumbai-devendra-fadnavis-flags-off-flood-relief-vehicles-to-jk-gallery/</t>
+          <t>https://www.lokmat.com/topics/ravindra-chavan/page/3/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/short-videos/ravindra-chavan-x-account-suspended/938586</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nanded/congress-mp-ravindra-chavan-from-nanded-criticize-bjp-mp-ashok-chavan/videoshow/123898698.cms</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/two-people-who-looted-a-petrol-pump-operator-in-chandur-were-caught-two-absconded/</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/amp/story/desh-videsh/charlie-kirk-shot-dead-at-utah-college-event</t>
+          <t>https://www.dainikprabhat.com/maval-political-shift-big-blow-to-maval-congress-hundreds-of-congress-workers-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/third-accused-in-robbery-case-arrested/</t>
+          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/bjp-provides-major-assistance-to-kashmir-flood-victims-first-wave-of-resource-trucks-depart/articleshow/123798265.cms</t>
+          <t>https://www.greaterkashmir.com/national/1-lakh-cataract-surgeries-in-maharashtra-to-mark-pms-birthday-bjp/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/gadchiroli/gadchiroli/gadchiroli-mla-narote-meets-bjp-state-president-15383461</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34557/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/thane/kalyan-dombivli-municipal-election-2025-new-political-equation-in-new-ward-system/132120/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/thane/page-9/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/videos/politics/madha-illegal-excavation-video-1476356.html</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B5-%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%B8%E0%A5%82-%E0%A4%85%E0%A4%A8%E0%A5%8D-rss-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%A4%E0%A4%B2%E0%A5%87-%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%87-%E0%A4%A8%E0%A4%B5%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1HLd3n?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/short-videos/chhagan-bhujbal-priase-cm-fadnavis/938587</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/internal-dispute-within-solapur-city-bjp-has-come-to-the-fore-988665.html/amp</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/cleanliness-drive-begins-in-kdmc-ward.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/madha-jai-malhar-kala-kendra-dispute-and-firing-one-injured-dk88</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-unveils-rs-3268-cr-avgc-xr-policy-to-create-2-lakh-jobs-23594327</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/rss-sarsanghchalak-mohan-bhagwat-statement-ticket-seekers-fear-dk88-rc70</t>
+          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modi-s-birthday-bjp/2919522</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/rlda-announces-tender-for-new-projects-while-csmt-station-redevelopment-remains-incomplete/articleshow/123798372.cms</t>
+          <t>https://www.ptinews.com/detail/national/One-lakh-cataract-surgeries-in-Maharashtra-to-mark-Modi-s-birthday-BJP/2919522</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/conditional-bail-granted-by-special-court-in-25-kg-cannabis-case/articleshow/123800360.cms</t>
+          <t>https://www.msn.com/hi-in/news/india/%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AC%E0%A4%A8%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A5%87%E0%A4%82%E0%A4%A7-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A5%87-%E0%A4%B9-%E0%A4%A6-%E0%A4%A8-%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B0-%E0%A4%88-%E0%A4%95%E0%A5%81%E0%A4%A3-%E0%A4%B2-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%95-%E0%A4%9C-%E0%A4%87%E0%A4%A8-%E0%A4%82%E0%A4%97/ar-AA1HO1X4?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/65-homes-eligible-in-dharavi-redevelopment-project-including-322-families/articleshow/123798304.cms</t>
+          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/chlorine-gas-leak-at-bhivandi-water-purification-center-five-employees-affected/articleshow/123798337.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%A4-%E0%A4%95-%E0%A4%B0-%E0%A4%9C%E0%A4%A8-%E0%A4%A4-%E0%A4%95%E0%A4%B0-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%B5%E0%A5%87%E0%A4%B7-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-bjp-%E0%A4%AE%E0%A4%B9-%E0%A4%A7-%E0%A4%B5%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%A8-%E0%A4%A4-%E0%A4%A8-%E0%A4%97%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A5%81%E0%A4%9B-%E0%A4%95%E0%A4%B9/ar-BB1rjuv7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/mumbai-to-develop-seven-sewage-treatment-plants-plan-to-discharge-treated-water-in-sea/articleshow/123798292.cms</t>
+          <t>https://statetimes.in/deportation-a-practical-approach-of-bringing-criminals-from-abroad-amit-shah/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/malegaon-bomb-blast-case-victims-families-challenge-acquittal-of-sadhvi-pragya-singh-thakur/articleshow/123800199.cms</t>
+          <t>https://www.etvbharat.com/en/!bharat/pm-modi-to-lay-foundation-of-pm-mitra-park-launch-sewa-pakhwada-in-madhya-pradesh-on-september-17-enn25091602243</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/india-must-be-force-for-global-good-rss-chief/articleshow/123816266.cms</t>
+          <t>https://www.devdiscourse.com/article/health/3629547-maharashtras-mega-health-drive-for-pm-modis-birthday?utm_campaign=Bundle&amp;utm_medium=referral&amp;utm_source=Bundle</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/amit-shah-at-lalbaugcha-raja-%E0%A4%97-%E0%A4%82%E0%A4%A1%E0%A4%B8-%E0%A4%A8-%E0%A4%A4%E0%A4%B5-%E0%A4%B2-%E0%A4%95%E0%A4%A1%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B2-%E0%A4%B2%E0%A4%AC-%E0%A4%97%E0%A4%9A-%E0%A4%B0-%E0%A4%9C-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%B2/ar-AA1LwAZa?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.devdiscourse.com/article/health/3629623-crisis-in-khyber-pakhtunkhwa-polio-team-kidnapped-amid-new-cases?amp</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.eaajkaanand.com/Encyc/2025/9/11/vote.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://thefocusindia.com/maharashtra-news/fadnavis-slams-thackeray-brothers-at-bjp-rally-284342/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://deshonnati.com/response-to-namo-yuva-run-marathon-in-parbhani/?amp=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/editor-detail/One-lakh-cataract-surgeries-in-Maharashtra-to-mark-Modi-s-birthday-BJP/2919522</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/on-the-occasion-of-modi-birthday-a-cleanliness-and-tree-plantation-campaign-was-organized-by-the-old-bjp-kalyan-city-committee-993381.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/stories-detail/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://newsarenaindia.com/nation/marking-pm-s-b-day-maha-bjp-plans-1-lakh-cataract-surgeries/56550</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/amp_articleshow/124001969.cms</t>
         </is>
       </c>
     </row>

--- a/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,252 +438,182 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/dombivli-mla-ravindra-chavan-to-be-appointed-maharashtra-bjp-prez/ar-AA1HJbtF?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.ptinews.com/editor-detail/One-lakh-cataract-surgeries-in-Maharashtra-to-mark-Modi-s-birthday-BJP/2919522</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%AB-%E0%A4%B8%E0%A5%87-%E0%A4%9F-%E0%A4%95%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A4%A3-%E0%A4%A4-%E0%A4%B2-%E0%A4%AE%E0%A4%A4%E0%A4%A6-%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B5%E0%A4%B3%E0%A4%B2%E0%A5%87-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B0-%E0%A4%A3%E0%A5%87-%E0%A4%95%E0%A5%81%E0%A4%9F%E0%A5%81%E0%A4%82%E0%A4%AC-%E0%A4%B8-%E0%A4%A0-%E0%A4%A7-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%98%E0%A4%82%E0%A4%9F/ar-AA1v1SPv?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.tarunbharat.com/spontaneous-response-to-telemedicine-clinic-camp-in-sangeli/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/topics/ravindra-chavan/page/3/</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nanded/congress-mp-ravindra-chavan-from-nanded-criticize-bjp-mp-ashok-chavan/videoshow/123898698.cms</t>
+          <t>https://www.marathi.hindusthanpost.com/social/bjps-big-announcement-grand-activities-will-be-held-across-the-state/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://www.dainikprabhat.com/maval-political-shift-big-blow-to-maval-congress-hundreds-of-congress-workers-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/maval-political-shift-big-blow-to-maval-congress-hundreds-of-congress-workers-join-bjp/</t>
+          <t>https://www.greaterkashmir.com/national/1-lakh-cataract-surgeries-in-maharashtra-to-mark-pms-birthday-bjp/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/national/1-lakh-cataract-surgeries-in-maharashtra-to-mark-pms-birthday-bjp/</t>
+          <t>https://newsarenaindia.com/nation/marking-pm-s-b-day-maha-bjp-plans-1-lakh-cataract-surgeries/56550</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
+          <t>https://www.uniindia.com/news/west/event-mah-modi-birthday-celebration/3580965.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/thackeray-brothers-meeting-fixed-on-dussehra-shivaji-park-alliance-buzz-sw79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B5-%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%B8%E0%A5%82-%E0%A4%85%E0%A4%A8%E0%A5%8D-rss-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%A4%E0%A4%B2%E0%A5%87-%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%87-%E0%A4%A8%E0%A4%B5%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1HLd3n?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/ajit-pawar-reacts-to-bhujbal-criticism-avoid-divide-in-society-sw79-rc70</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/jayant-patil-ncp-sangli-padalkar-sw79-rg93</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/cleanliness-drive-begins-in-kdmc-ward.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-unveils-rs-3268-cr-avgc-xr-policy-to-create-2-lakh-jobs-23594327</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modi-s-birthday-bjp/2919522</t>
+          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/One-lakh-cataract-surgeries-in-Maharashtra-to-mark-Modi-s-birthday-BJP/2919522</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/shiv-sena-jolts-bjp-in-ulhasnagar-allies-with-sai-party/articleshow/124046213.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/india/%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AC%E0%A4%A8%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A5%87%E0%A4%82%E0%A4%A7-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A5%87-%E0%A4%B9-%E0%A4%A6-%E0%A4%A8-%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B0-%E0%A4%88-%E0%A4%95%E0%A5%81%E0%A4%A3-%E0%A4%B2-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%95-%E0%A4%9C-%E0%A4%87%E0%A4%A8-%E0%A4%82%E0%A4%97/ar-AA1HO1X4?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
+          <t>https://mahasamvad.in/179272/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%A4-%E0%A4%95-%E0%A4%B0-%E0%A4%9C%E0%A4%A8-%E0%A4%A4-%E0%A4%95%E0%A4%B0-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%B5%E0%A5%87%E0%A4%B7-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-bjp-%E0%A4%AE%E0%A4%B9-%E0%A4%A7-%E0%A4%B5%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%A8-%E0%A4%A4-%E0%A4%A8-%E0%A4%97%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A5%81%E0%A4%9B-%E0%A4%95%E0%A4%B9/ar-BB1rjuv7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://statetimes.in/deportation-a-practical-approach-of-bringing-criminals-from-abroad-amit-shah/</t>
+          <t>https://www.saamana.com/maharashtra-20-lakhs-spent-from-government-treasury-in-the-name-of-washing-sheets-and-curtains-in-a-worli-rest-house/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/pm-modi-to-lay-foundation-of-pm-mitra-park-launch-sewa-pakhwada-in-madhya-pradesh-on-september-17-enn25091602243</t>
+          <t>https://mahasamvad.in/179534/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/health/3629547-maharashtras-mega-health-drive-for-pm-modis-birthday?utm_campaign=Bundle&amp;utm_medium=referral&amp;utm_source=Bundle</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/mumbais-mayor-will-be-for-mumbaikars-not-for-the-chair-cm-devendra-fadnavis-attack/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/health/3629623-crisis-in-khyber-pakhtunkhwa-polio-team-kidnapped-amid-new-cases?amp</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>https://thefocusindia.com/maharashtra-news/fadnavis-slams-thackeray-brothers-at-bjp-rally-284342/</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>https://deshonnati.com/response-to-namo-yuva-run-marathon-in-parbhani/?amp=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/editor-detail/One-lakh-cataract-surgeries-in-Maharashtra-to-mark-Modi-s-birthday-BJP/2919522</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>https://www.navarashtra.com/maharashtra/on-the-occasion-of-modi-birthday-a-cleanliness-and-tree-plantation-campaign-was-organized-by-the-old-bjp-kalyan-city-committee-993381.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/stories-detail/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
           <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>https://newsarenaindia.com/nation/marking-pm-s-b-day-maha-bjp-plans-1-lakh-cataract-surgeries/56550</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/amp_articleshow/124001969.cms</t>
         </is>
       </c>
     </row>

--- a/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,182 +438,161 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/One-lakh-cataract-surgeries-in-Maharashtra-to-mark-Modi-s-birthday-BJP/2919522</t>
+          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modi-s-birthday-bjp/2919522</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/spontaneous-response-to-telemedicine-clinic-camp-in-sangeli/</t>
+          <t>https://www.loksatta.com/thane/birthday-of-dombivli-mla-ravindra-chavan-phm-00-5386678/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/shiv-sena-jolts-bjp-in-ulhasnagar-allies-with-sai-party/articleshow/124046213.cms</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/bjps-big-announcement-grand-activities-will-be-held-across-the-state/</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/maval-political-shift-big-blow-to-maval-congress-hundreds-of-congress-workers-join-bjp/</t>
+          <t>https://aaplaawajnews.com/2025/34569/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/national/1-lakh-cataract-surgeries-in-maharashtra-to-mark-pms-birthday-bjp/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
+          <t>https://www.hindustantimes.com/india-news/how-bjp-is-celebrating-pm-narendra-modis-75th-birthday-across-states-today-details-of-events-101758067171247.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://newsarenaindia.com/nation/marking-pm-s-b-day-maha-bjp-plans-1-lakh-cataract-surgeries/56550</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/news/west/event-mah-modi-birthday-celebration/3580965.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/thackeray-brothers-meeting-fixed-on-dussehra-shivaji-park-alliance-buzz-sw79</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/ajit-pawar-reacts-to-bhujbal-criticism-avoid-divide-in-society-sw79-rc70</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/thackeray-brothers-meeting-fixed-on-dussehra-shivaji-park-alliance-buzz-sw79</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/jayant-patil-ncp-sangli-padalkar-sw79-rg93</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/ajit-pawar-reacts-to-bhujbal-criticism-avoid-divide-in-society-sw79-rc70</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/jayant-patil-ncp-sangli-padalkar-sw79-rg93</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
+          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
+          <t>https://www.ptinews.com/stories-detail/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522/1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
+          <t>https://mahasamvad.in/179272/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/shiv-sena-jolts-bjp-in-ulhasnagar-allies-with-sai-party/articleshow/124046213.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522</t>
+          <t>https://civicmirror.in/maharashtra/new-gst-reforms-will-give-new-impetus-to-indias-economic-development-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179272/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/mumbais-mayor-will-be-for-mumbaikars-not-for-the-chair-cm-devendra-fadnavis-attack/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/maharashtra-20-lakhs-spent-from-government-treasury-in-the-name-of-washing-sheets-and-curtains-in-a-worli-rest-house/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179534/</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/mumbais-mayor-will-be-for-mumbaikars-not-for-the-chair-cm-devendra-fadnavis-attack/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
+          <t>https://m.economictimes.com/news/india/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/articleshow/123921237.cms</t>
         </is>
       </c>
     </row>

--- a/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,35 +438,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modi-s-birthday-bjp/2919522</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/birthday-of-dombivli-mla-ravindra-chavan-phm-00-5386678/</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/shiv-sena-jolts-bjp-in-ulhasnagar-allies-with-sai-party/articleshow/124046213.cms</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/shiv-sena-jolts-bjp-in-ulhasnagar-allies-with-sai-party/articleshow/124046213.cms</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://aaplaawajnews.com/2025/34569/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34569/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
         </is>
       </c>
     </row>
@@ -480,21 +480,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/how-bjp-is-celebrating-pm-narendra-modis-75th-birthday-across-states-today-details-of-events-101758067171247.html</t>
+          <t>https://www.greaterkashmir.com/national/1-lakh-cataract-surgeries-in-maharashtra-to-mark-pms-birthday-bjp/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
+          <t>https://www.newsdrum.in/national/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday-10469982</t>
         </is>
       </c>
     </row>
@@ -508,14 +508,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/ajit-pawar-reacts-to-bhujbal-criticism-avoid-divide-in-society-sw79-rc70</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/jayant-patil-ncp-sangli-padalkar-sw79-rg93</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/jayant-patil-ncp-sangli-padalkar-sw79-rg93</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
@@ -529,42 +529,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
+          <t>https://marathi.ndtv.com/videos/how-will-raj-thackeray-ambarnath-and-kalyan-daura-be-ndtv-report-996461</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
+          <t>https://marathi.ndtv.com/videos/obc-elgar-morcha-in-hingoli-laxman-hake-warm-welcome-995642</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/stories-detail/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522/1</t>
+          <t>https://udayavani.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-131344?lang=en</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179272/</t>
+          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
+          <t>https://mahasamvad.in/179272/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/new-gst-reforms-will-give-new-impetus-to-indias-economic-development-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
         </is>
       </c>
     </row>
@@ -591,6 +591,13 @@
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>https://m.economictimes.com/news/india/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/articleshow/123921237.cms</t>
         </is>

--- a/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,161 +445,147 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/shiv-sena-jolts-bjp-in-ulhasnagar-allies-with-sai-party/articleshow/124046213.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://udayavani.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-131344?lang=en</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34569/</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/shiv-sena-jolts-bjp-in-ulhasnagar-allies-with-sai-party/articleshow/124046213.cms</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
+          <t>https://deshdoot.com/container-hit-vehicles-loss-ahilyanagar/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/national/1-lakh-cataract-surgeries-in-maharashtra-to-mark-pms-birthday-bjp/</t>
+          <t>https://aaplaawajnews.com/2025/34569/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday-10469982</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/thackeray-brothers-meeting-fixed-on-dussehra-shivaji-park-alliance-buzz-sw79</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/jayant-patil-ncp-sangli-padalkar-sw79-rg93</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/thackeray-brothers-meeting-fixed-on-dussehra-shivaji-park-alliance-buzz-sw79</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
+          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/how-will-raj-thackeray-ambarnath-and-kalyan-daura-be-ndtv-report-996461</t>
+          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/obc-elgar-morcha-in-hingoli-laxman-hake-warm-welcome-995642</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/mumbai-civic-polls-uddhav-raj-thackeray-alliance-vs-shinde-sena-sw79</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://udayavani.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-131344?lang=en</t>
+          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
+          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179272/</t>
+          <t>https://deshdoot.com/mp-supriya-sule-visited-trimbakeshwar-and-take-darshan-trimbakraj-temple/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+          <t>https://www.hindustantimes.com/india-news/how-bjp-is-celebrating-pm-narendra-modis-75th-birthday-across-states-today-details-of-events-101758067171247.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/mumbais-mayor-will-be-for-mumbaikars-not-for-the-chair-cm-devendra-fadnavis-attack/</t>
+          <t>https://m.economictimes.com/news/india/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/articleshow/123921237.cms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/india/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/articleshow/123921237.cms</t>
+          <t>https://www.dailyexcelsior.com/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
         </is>
       </c>
     </row>

--- a/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links_Ravindra Chavan_failed_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,14 +445,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://udayavani.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-131344?lang=en</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
         </is>
       </c>
     </row>
@@ -501,91 +501,77 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
+          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/thackeray-brothers-meeting-fixed-on-dussehra-shivaji-park-alliance-buzz-sw79</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/mumbai-civic-polls-uddhav-raj-thackeray-alliance-vs-shinde-sena-sw79</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
+          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/mumbai-civic-polls-uddhav-raj-thackeray-alliance-vs-shinde-sena-sw79</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
+          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
+          <t>https://www.hindustantimes.com/india-news/how-bjp-is-celebrating-pm-narendra-modis-75th-birthday-across-states-today-details-of-events-101758067171247.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/mp-supriya-sule-visited-trimbakeshwar-and-take-darshan-trimbakraj-temple/</t>
+          <t>https://m.economictimes.com/news/india/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/articleshow/123921237.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
+          <t>https://www.dailyexcelsior.com/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/how-bjp-is-celebrating-pm-narendra-modis-75th-birthday-across-states-today-details-of-events-101758067171247.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/india/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/articleshow/123921237.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>https://www.dailyexcelsior.com/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
+          <t>https://www.newsdanka.com/vishesh/state-bjp-to-organize-a-seva-pandharwada-for-pm-modis-75th-birthday/167436/</t>
         </is>
       </c>
     </row>
